--- a/demo_11626_FINAL_READY.xlsx
+++ b/demo_11626_FINAL_READY.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shivam220802\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96437654-D318-4F46-9755-D31B21CC89A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="811">
   <si>
     <t>Transcripts</t>
   </si>
@@ -4249,12 +4255,3393 @@
   <si>
     <t>High Scoring</t>
   </si>
+  <si>
+    <t>" AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon
+     AGENT
+     00:00:10
+     I'm so sorry to hear that you're experiencing poor audio quality. Can you tell me more about the issue you're facing?
+     CUSTOMER
+     00:00:17
+     yeah... the audio is really bad... i can barely hear what the other person is saying
+     AGENT
+     00:00:24
+     I apologize for the inconvenience. Have you tried restarting the application or checking your internet connection?
+     CUSTOMER
+     00:00:31
+     yeah... i've tried that... it didn't work
+     AGENT
+     00:00:36
+     Okay, let me see what else I can do to help you. Can you please confirm your username so I can look into this further?
+     CUSTOMER
+     00:00:43
+     it's... uh... johndoe123
+     AGENT
+     00:00:49
+     Thank you, John. I've checked on our end and it seems like there might be an issue with our servers. I'm going to go ahead and escalate this to our technical team to get it resolved as soon as possible.
+     CUSTOMER
+     00:01:00
+     okay... thanks
+     AGENT
+     00:01:04
+     You're welcome, John. I apologize again for the poor audio quality. We'll get this resolved for you. Is there anything else I can assist you with in the meantime?
+     CUSTOMER
+     00:01:11
+     no... that's it
+     AGENT
+     00:01:14
+     Alright, John. I'll go ahead and close this ticket. You should receive an update from our technical team soon. Thank you for your patience and understanding.
+     CUSTOMER
+     00:01:20
+     thanks... bye
+     AGENT
+     00:01:23
+     You're welcome, John. Have a great day. Bye.
+     "</t>
+  </si>
+  <si>
+    <t>7.0</t>
+  </si>
+  <si>
+    <t>The customer's language and tone throughout the conversation are calm and factual, without expressing a clear emotional tone. They report a problem, provide information, and respond to the agent's questions without showing signs of strong emotions like joy, sadness, anger, fear, disgust, or surprise.</t>
+  </si>
+  <si>
+    <t>transcript51</t>
+  </si>
+  <si>
+    <t>The customer experienced poor audio quality and was assisted by the agent in troubleshooting the issue. The agent escalated the problem to the technical team and closed the ticket, with the customer receiving an update soon.</t>
+  </si>
+  <si>
+    <t>audio is really bad... i can barely hear what the other person is saying</t>
+  </si>
+  <si>
+    <t>Customer is frustrated with the poor audio quality, but the agent is apologetic and helpful in resolving the issue, which reduces the churn risk to low.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon. I'm having some issues with my laptop. The keyboard is not working properly.
+     AGENT
+     00:00:15
+     Sorry to hear that. Can you please tell me more about the issue you're experiencing with your keyboard?
+     CUSTOMER
+     00:00:22
+     Yeah, sometimes the keys don't register when I press them, and sometimes they register multiple times. It's really frustrating.
+     AGENT
+     00:00:30
+     I understand how frustrating that can be. Have you tried restarting your laptop or updating your keyboard drivers?
+     CUSTOMER
+     00:00:38
+     Yeah, I've tried restarting, but I'm not sure about the drivers. I'm not very tech-savvy.
+     AGENT
+     00:00:45
+     No worries, I can walk you through it. Can you please tell me what operating system you're using on your laptop?
+     CUSTOMER
+     00:00:52
+     I'm using Windows 10.
+     AGENT
+     00:00:58
+     Okay, I'll guide you through the process of updating your keyboard drivers. Can you please go to your device manager and click on keyboards?
+     CUSTOMER
+     00:01:05
+     Okay, I'm there.
+     AGENT
+     00:01:10
+     Great! Now, can you please right-click on the keyboard device and select update driver?
+     CUSTOMER
+     00:01:17
+     Okay, I've done that.
+     AGENT
+     00:01:23
+     Now, your laptop should search for and install any available updates. This might take a few minutes.
+     CUSTOMER
+     00:01:30
+     Okay, it's done.
+     AGENT
+     00:01:35
+     Great! Can you please try using your keyboard now and see if the issue is resolved?
+     CUSTOMER
+     00:01:42
+     Yeah, it seems to be working now. Thanks so much for your help!
+     AGENT
+     00:01:48
+     You're welcome! I'm glad I could assist you in resolving the issue. If you have any other problems or concerns, please don't hesitate to reach out to us.
+     CUSTOMER
+     00:01:55
+     Will do, thanks again.
+     AGENT
+     00:02:00
+     You're welcome! Have a great day!"</t>
+  </si>
+  <si>
+    <t>8.0</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration and annoyance with the keyboard issue, using words like'really frustrating' and 'it's really frustrating'. This indicates a strong negative emotion, which is best described as anger.</t>
+  </si>
+  <si>
+    <t>transcript52</t>
+  </si>
+  <si>
+    <t>Customer's laptop keyboard was not working properly due to driver issues. Agent guided the customer through updating the keyboard drivers, which resolved the issue.</t>
+  </si>
+  <si>
+    <t>The customer's issue was resolved, and they expressed gratitude towards the agent. There was no indication of churn or dissatisfaction with the company.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon
+     AGENT
+     00:00:10
+     How can I assist you today?
+     CUSTOMER
+     00:00:15
+     I'm having some issues with my internet connection. It's been slow and intermittent lately.
+     AGENT
+     00:00:22
+     Sorry to hear that. Can you tell me more about the issue you're experiencing? When did it start?
+     CUSTOMER
+     00:00:30
+     It started about a week ago. I've tried restarting my router but it doesn't seem to make a difference.
+     AGENT
+     00:00:38
+     Okay, I'm going to check on the status of our network in your area. Can you please confirm your account information so I can look into this further?
+     CUSTOMER
+     00:00:45
+     Yeah, my account number is 123456.
+     AGENT
+     00:00:52
+     Thank you. I've checked on our network and it appears that there's an outage in your area. Our team is working to resolve the issue as soon as possible.
+     CUSTOMER
+     00:01:00
+     Okay, that's good to know. Do you have an estimated time of resolution?
+     AGENT
+     00:01:05
+     We're estimating that the issue will be resolved within the next 24 hours. I apologize for the inconvenience this has caused.
+     CUSTOMER
+     00:01:12
+     Alright, thank you for letting me know. I appreciate your help.
+     AGENT
+     00:01:18
+     You're welcome. If you have any further issues or concerns, please don't hesitate to reach out to us. Have a great day.
+     CUSTOMER
+     00:01:25
+     You too, thank you."</t>
+  </si>
+  <si>
+    <t>The customer's tone is calm and factual throughout the conversation, with a focus on describing the issue and seeking resolution. They express appreciation for the agent's help, but do not display strong emotions such as joy, sadness, anger, or fear.</t>
+  </si>
+  <si>
+    <t>transcript53</t>
+  </si>
+  <si>
+    <t>Customer reported slow and intermittent internet connection. Agent checked network status and confirmed outage in customer's area. Estimated resolution time was 24 hours. Agent apologized for inconvenience and provided customer support.</t>
+  </si>
+  <si>
+    <t>I'm having some issues with my internet connection. It's been slow and intermittent lately.</t>
+  </si>
+  <si>
+    <t>The customer is experiencing frustration with their internet connection, but the issue is being addressed by the agent and the customer's tone is not overly angry or aggressive, indicating a low churn risk.</t>
+  </si>
+  <si>
+    <t>"AGENT
+00:00:00
+Hello good afternoon.
+CUSTOMER
+00:00:07
+good afternoon. I'm having some trouble with my computer. The audio isn't working.
+AGENT
+00:00:14
+Sorry to hear that. Can you tell me a little bit more about what's going on? When did the audio stop working?
+CUSTOMER
+00:00:23
+It just stopped working all of a sudden. I was watching a video and then it just went silent.
+AGENT
+00:00:31
+Okay. Have you tried restarting your computer or checking the audio settings to make sure they're turned up?
+CUSTOMER
+00:00:40
+Yeah, I've tried all that. I've even checked the cables to make sure they're plugged in properly.
+AGENT
+00:00:48
+Okay. In that case, it's possible that there's a problem with your audio driver. I can walk you through the steps to update it if you'd like.
+CUSTOMER
+00:00:57
+That sounds like it might work. But I'm not very tech-savvy, so you'll have to talk me through it slowly.
+AGENT
+00:01:04
+No problem at all. I'll walk you through it step by step. First, can you click on the Start menu and then click on the Control Panel?
+CUSTOMER
+00:01:15
+Okay... got it.
+AGENT
+00:01:20
+Great. Now, can you click on the Device Manager?
+CUSTOMER
+00:01:26
+Yeah... I see it.
+AGENT
+00:01:31
+Okay. Now, can you expand the Sound, video and game controllers section?
+CUSTOMER
+00:01:39
+Okay... done.
+AGENT
+00:01:44
+Great. Now, can you right-click on the audio device and select Update driver?
+CUSTOMER
+00:01:52
+Okay... I think I did it.
+AGENT
+00:01:58
+Great! Your audio driver should now be updated. Can you try playing some audio to see if it's working again?
+CUSTOMER
+00:02:05
+Yeah... it's working! Thank you so much for your help!
+AGENT
+00:02:11
+You're welcome! I'm glad I could assist you in getting your audio working again. Is there anything else I can help you with today?
+CUSTOMER
+00:02:18
+No, that's all. Thanks again for your help.
+AGENT
+00:02:23
+You're welcome! Have a great day!"</t>
+  </si>
+  <si>
+    <t>The customer expresses happiness and relief when the issue is resolved, and they thank the agent for their help.</t>
+  </si>
+  <si>
+    <t>transcript54</t>
+  </si>
+  <si>
+    <t>The customer was experiencing issues with their computer's audio not working. The agent helped the customer troubleshoot the problem by checking the audio settings and updating the audio driver. The customer was able to resolve the issue and the audio was working again.</t>
+  </si>
+  <si>
+    <t>" AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon. I'm having some issues with my internet connection. It's been really slow lately and I'm not sure what's going on.
+     AGENT
+     00:00:15
+     Sorry to hear that. Can you tell me a little bit more about what's been going on? When did you first notice the slow speeds?
+     CUSTOMER
+     00:00:23
+     Yeah, it started about a week ago. I was trying to stream a movie and it kept buffering. I thought it was just the movie, but then I tried to load some web pages and they were taking forever to load.
+     AGENT
+     00:00:35
+     Okay, that sounds frustrating. Have you tried restarting your router or modem at all?
+     CUSTOMER
+     00:00:42
+     Yeah, I've tried that a few times. It seems to work for a little bit, but then the speeds go back to being slow.
+     AGENT
+     00:00:50
+     Okay. In that case, I'd like to run some tests on your connection to see if we can identify the issue. Can you please confirm your account information so I can access your account?
+     CUSTOMER
+     00:00:58
+     Yeah, my account number is 123456.
+     AGENT
+     00:01:03
+     Thank you. I'm going to go ahead and run those tests. Can you please hold for just a minute?
+     CUSTOMER
+     00:01:10
+     Okay.
+     AGENT
+     00:01:20
+     Okay, I've run the tests and it looks like there's an issue with the connection in your area. I'm going to go ahead and send a technician to your location to investigate further.
+     CUSTOMER
+     00:01:30
+     Okay, that sounds good. When can I expect them to arrive?
+     AGENT
+     00:01:35
+     We can schedule the appointment for tomorrow afternoon. Would that work for you?
+     CUSTOMER
+     00:01:40
+     Yeah, that works for me.
+     AGENT
+     00:01:45
+     Great. I'll go ahead and schedule that. You should receive a confirmation email with the details. Is there anything else I can assist you with today?
+     CUSTOMER
+     00:01:50
+     No, that's all. Thanks for your help.
+     AGENT
+     00:01:55
+     You're welcome. We'll get that issue resolved for you as soon as possible. Have a great day.
+     CUSTOMER
+     00:02:00
+     You too.
+     "</t>
+  </si>
+  <si>
+    <t>The customer's tone is calm and factual throughout the conversation, expressing frustration and disappointment with the slow internet connection, but also cooperation and understanding when discussing the issue and the solution.</t>
+  </si>
+  <si>
+    <t>transcript55</t>
+  </si>
+  <si>
+    <t>Customer reported slow internet speeds, which started a week ago. Agent ran tests and identified an issue with the connection in the customer's area. Technician was scheduled to visit the customer's location the next day to investigate further.</t>
+  </si>
+  <si>
+    <t>it kept buffering. I thought it was just the movie, but then I tried to load some web pages and they were taking forever to load.</t>
+  </si>
+  <si>
+    <t>The customer is frustrated with the slow internet connection, but the agent is able to resolve the issue and schedule a technician visit, which reduces the churn risk to low.</t>
+  </si>
+  <si>
+    <t>" AGENT
+       00:00:00
+       Hello good afternoon.
+       CUSTOMER
+       00:00:07
+       good afternoon
+       AGENT
+       00:00:10
+       How can I assist you today?
+       CUSTOMER
+       00:00:15
+       I'm having some issues with my internet connection. It keeps dropping out.
+       AGENT
+       00:00:20
+       Sorry to hear that. Can you please tell me more about the issue? When did it start happening?
+       CUSTOMER
+       00:00:25
+       It started yesterday evening. I was in the middle of a project and suddenly I lost connection.
+       AGENT
+       00:00:30
+       Okay. Have you tried restarting your router or modem?
+       CUSTOMER
+       00:00:35
+       Yeah, I've tried that a few times but it doesn't seem to make a difference.
+       AGENT
+       00:00:40
+       Alright. Let me check on our end to see if there are any outages in your area. Can you please provide me with your account information?
+       CUSTOMER
+       00:00:45
+       Sure. My account number is 123456.
+       AGENT
+       00:00:50
+       Thank you. I've checked and it looks like there was a brief outage in your area yesterday evening. But it should be resolved now.
+       CUSTOMER
+       00:00:55
+       Okay, that's good to know. But I'm still having issues. What else can I try?
+       AGENT
+       00:01:00
+       I'd like to troubleshoot further. Can you please try connecting to a different device or a different network to see if the issue persists?
+       CUSTOMER
+       00:01:05
+       Okay, I'll try that.
+       AGENT
+       00:01:10
+       Also, I'd like to send a technician to your location to investigate further. Would you be available for a visit tomorrow or the day after?
+       CUSTOMER
+       00:01:15
+       Yeah, tomorrow would be fine.
+       AGENT
+       00:01:20
+       Great. I've scheduled a technician visit for tomorrow. You should receive a confirmation email with the details. Is there anything else I can assist you with today?
+       CUSTOMER
+       00:01:25
+       No, that's all. Thanks for your help.
+       AGENT
+       00:01:30
+       You're welcome. We'll get your internet connection up and running smoothly again. Have a great day!
+       CUSTOMER
+       00:01:35
+       Thanks, you too.
+       "</t>
+  </si>
+  <si>
+    <t>The customer's tone is calm and factual throughout the conversation, with a focus on resolving the issue with their internet connection. They express frustration and disappointment with the ongoing problem, but their language remains neutral and objective.</t>
+  </si>
+  <si>
+    <t>transcript56</t>
+  </si>
+  <si>
+    <t>The customer reported issues with their internet connection, which dropped out yesterday evening. The agent checked for outages in the area and found a brief outage, but the issue persisted. The agent scheduled a technician visit for the next day to further investigate and resolve the issue.</t>
+  </si>
+  <si>
+    <t>The customer is calling about an issue with their internet connection, but the agent is able to assist and resolve the issue. The customer's tone is not angry or frustrated, and there is no mention of switching companies.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon
+     AGENT
+     00:00:10
+     How can I assist you today?
+     CUSTOMER
+     00:00:15
+     I'm having some issues with my phone's battery. It's been draining really fast lately.
+     AGENT
+     00:00:22
+     Sorry to hear that. Can you tell me more about the issue? How long has this been happening?
+     CUSTOMER
+     00:00:30
+     It started about a week ago. I've tried closing some apps and turning off location services, but nothing seems to be working.
+     AGENT
+     00:00:40
+     Have you tried restarting your phone in safe mode or doing a factory reset?
+     CUSTOMER
+     00:00:47
+     No, I haven't tried that yet. I'm not really tech-savvy, so I'm not sure how to do that.
+     AGENT
+     00:00:55
+     Don't worry, I can guide you through it. Let me walk you through the steps. 
+     CUSTOMER
+     00:01:02
+     Okay, that would be great. Thank you.
+     AGENT
+     00:01:07
+     So, first, let's try restarting your phone in safe mode. This will disable all third-party apps and help us determine if one of them is causing the issue. 
+     CUSTOMER
+     00:01:17
+     Okay, I think I did it. But how do I know if it's working?
+     AGENT
+     00:01:24
+     If your battery life improves in safe mode, it could indicate that a third-party app is causing the issue. If the problem persists, we may need to do a factory reset. 
+     CUSTOMER
+     00:01:35
+     Okay, I'll try that. But what if it's a hardware issue? Can you replace the battery or something?
+     AGENT
+     00:01:43
+     If it's a hardware issue, we can definitely look into replacing the battery or repairing your phone. But let's try the software troubleshooting steps first. 
+     CUSTOMER
+     00:01:52
+     Okay, that sounds good. Thank you for your help.
+     AGENT
+     00:01:58
+     You're welcome! If you have any more issues or concerns, feel free to reach out to us anytime. Have a great day!
+     CUSTOMER
+     00:02:04
+     You too, thank you."</t>
+  </si>
+  <si>
+    <t>The customer's tone is calm and factual throughout the conversation, with a focus on describing the issue and seeking help. They express gratitude and appreciation for the agent's assistance, but do not show strong emotions such as joy, sadness, anger, fear, disgust, or surprise.</t>
+  </si>
+  <si>
+    <t>transcript57</t>
+  </si>
+  <si>
+    <t>The customer is calling about a specific issue with their phone's battery, and the agent is able to assist them with troubleshooting steps. The customer's tone is polite and appreciative, and there is no indication of frustration or dissatisfaction that would suggest churn.</t>
+  </si>
+  <si>
+    <t>" AGENT
+       00:00:00
+       Hello good afternoon.
+       CUSTOMER
+       00:00:07
+       good afternoon. I'm having some issues with my internet connection. It's been dropping out constantly throughout the day.
+       AGENT
+       00:00:15
+       Sorry to hear that. Can you please tell me more about the issue you're experiencing? What kind of error messages are you seeing?
+       CUSTOMER
+       00:00:25
+       I'm not seeing any error messages, it just keeps disconnecting. I've tried restarting my router but it doesn't seem to make a difference.
+       AGENT
+       00:00:35
+       Okay, let me see what I can do to help you. Can you please confirm your account details so I can look into this further?
+       CUSTOMER
+       00:00:45
+       Yeah, my account number is 123456. But I'm getting really frustrated with this issue. I need a reliable connection for work.
+       AGENT
+       00:00:55
+       I completely understand, and I apologize again for the inconvenience. I've checked on your account and it looks like there's an outage in your area. Our team is working on it, but I can offer you a temporary solution to get you back online.
+       CUSTOMER
+       00:01:05
+       What's the temporary solution? And how long until the outage is fixed?
+       AGENT
+       00:01:15
+       We can provide you with a mobile hotspot device that will give you a stable connection until the outage is resolved. As for the outage, our team is working on it and we expect it to be resolved within the next 24-48 hours.
+       CUSTOMER
+       00:01:25
+       Okay, that sounds like it might work. But I'm still not happy about this. I've been with this company for years and I expect better service.
+       AGENT
+       00:01:35
+       I completely understand, and I apologize again for the issue. I'm going to go ahead and process the mobile hotspot device for you, and I'll also give you a credit on your next bill for the inconvenience.
+       CUSTOMER
+       00:01:45
+       Okay, thank you. I appreciate that.
+       AGENT
+       00:01:50
+       You're welcome. Is there anything else I can assist you with today?
+       CUSTOMER
+       00:01:55
+       No, that's all. Thank you for your help.
+       AGENT
+       00:02:00
+       You're welcome. Have a great day.
+       CUSTOMER
+       00:02:05
+       You too.
+       "</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration and disappointment with the service, using phrases like 'I'm getting really frustrated' and 'I've been with this company for years and I expect better service'. The customer's tone is negative and critical, indicating anger.</t>
+  </si>
+  <si>
+    <t>transcript58</t>
+  </si>
+  <si>
+    <t>Customer reported internet connection issues due to an outage in their area. Agent offered a temporary solution with a mobile hotspot device and a credit on their next bill. Customer was satisfied with the resolution and apologized for the inconvenience.</t>
+  </si>
+  <si>
+    <t>I've been with this company for years and I expect better service.</t>
+  </si>
+  <si>
+    <t>The customer is frustrated with the service and expresses disappointment, but the issue is resolved and the agent provides a credit on the next bill, which reduces the churn risk to low.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon, I'm having some issues with my phone's battery. It's been draining really fast and I'm worried it might be a defect.
+     AGENT
+     00:00:15
+     Sorry to hear that. Can you tell me more about the issue you're experiencing? How long has this been going on?
+     CUSTOMER
+     00:00:23
+     It started about a week ago. I've tried closing some apps and turning off location services, but nothing seems to be working. I'm getting really frustrated.
+     AGENT
+     00:00:32
+     I understand your concern. Have you tried restarting your phone in safe mode or doing a factory reset?
+     CUSTOMER
+     00:00:40
+     Yeah, I've tried restarting in safe mode, but it didn't make a difference. I'm not sure about doing a factory reset, I don't want to lose all my data.
+     AGENT
+     00:00:48
+     I completely understand. In that case, I'd like to troubleshoot further. Can you tell me what kind of usage you've had on your phone recently? Have you installed any new apps or updated your operating system?
+     CUSTOMER
+     00:00:57
+     I've been using my phone a lot for work, so I've had a lot of emails and messages coming in. And yeah, I did update my operating system a few days ago.
+     AGENT
+     00:01:05
+     Okay, that might be the culprit. Sometimes updates can cause issues with battery life. Let me check on some possible solutions for you. (pause) Okay, I've checked and it looks like there's a patch available that might fix the issue. Would you like me to guide you through the process of installing it?
+     CUSTOMER
+     00:01:20
+     Yeah, that sounds good. But what if it doesn't work? I'm really worried about having to replace my phone.
+     AGENT
+     00:01:28
+     I completely understand your concern. If the patch doesn't work, we can explore other options, including replacing your phone if it's defective. But let's try the patch first and see if it resolves the issue.
+     CUSTOMER
+     00:01:36
+     Okay, that sounds good. Can you walk me through the process of installing the patch?
+     AGENT
+     00:01:43
+     Absolutely. First, go to your settings app and click on 'About Phone'. Then, click on 'System Update' and it should prompt you to download and install the patch. If you have any issues or questions, feel free to ask.
+     CUSTOMER
+     00:01:54
+     Okay, got it. Thanks for your help. I'll try that and see if it works.
+     AGENT
+     00:02:00
+     You're welcome. If you have any further issues or concerns, don't hesitate to reach out to us. We're here to help. Have a great day!
+     CUSTOMER
+     00:02:06
+     Thanks, you too."</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration and annoyance throughout the conversation, particularly when discussing the battery issue and the potential need to replace their phone. They use phrases like 'I'm getting really frustrated' and 'I'm really worried about having to replace my phone', indicating a strong negative emotion.</t>
+  </si>
+  <si>
+    <t>transcript59</t>
+  </si>
+  <si>
+    <t>The customer was experiencing a fast-draining battery issue with their phone, which started about a week ago. The agent helped troubleshoot the issue by asking about recent usage and updates. The agent discovered a patch that might fix the issue and guided the customer through the process of installing it. The customer was concerned about replacing their phone, but the agent assured them that they would explore other options if the patch didn't work.</t>
+  </si>
+  <si>
+    <t>I'm getting really frustrated</t>
+  </si>
+  <si>
+    <t>The customer is frustrated with the battery issue, but the agent is able to troubleshoot and provide a solution, which reduces the risk of churn.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon. I'm having some issues with my battery, it's been draining really fast lately.
+     AGENT
+     00:00:15
+     Sorry to hear that. Can you tell me more about the issue you're experiencing? How long has this been going on?
+     CUSTOMER
+     00:00:25
+     Yeah, it started about a week ago. I've tried closing some apps and turning off location services, but nothing seems to be working.
+     AGENT
+     00:00:35
+     I see. Have you tried restarting your device or checking for any software updates?
+     CUSTOMER
+     00:00:43
+     Yeah, I've tried restarting it, but I haven't checked for updates. I'll try that now.
+     AGENT
+     00:00:50
+     Okay, go ahead and check for updates. If that doesn't work, we can try some other troubleshooting steps.
+     CUSTOMER
+     00:01:00
+     Okay, I just checked and there are no updates available. What's the next step?
+     AGENT
+     00:01:08
+     Alright, let's try to reset your device's settings. This will reset all of your device's settings to their default values.
+     CUSTOMER
+     00:01:18
+     Okay, I'll try that. But I'm getting a bit frustrated, I've had this device for less than a year and I'm already having issues.
+     AGENT
+     00:01:28
+     I understand your frustration. I apologize for the inconvenience. If resetting the settings doesn't work, we can look into replacing the battery or the device itself.
+     CUSTOMER
+     00:01:38
+     Okay, I'll try that. But can you also look into why this is happening? I don't want to have to deal with this again in the future.
+     AGENT
+     00:01:48
+     Absolutely, I'll make a note to have our technical team look into the issue. We'll also send you a follow-up email to ensure the issue is resolved.
+     CUSTOMER
+     00:02:00
+     Okay, thank you. I appreciate your help.
+     AGENT
+     00:02:05
+     You're welcome. Is there anything else I can assist you with today?
+     CUSTOMER
+     00:02:10
+     No, that's all. Thank you again.
+     AGENT
+     00:02:15
+     You're welcome. Have a great day.
+     CUSTOMER
+     00:02:20
+     You too."</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration and annoyance throughout the conversation, particularly when discussing the battery issue and the inconvenience it has caused. The customer's tone is also slightly aggressive when asking for a solution and expressing concern about the issue happening again in the future.</t>
+  </si>
+  <si>
+    <t>transcript60</t>
+  </si>
+  <si>
+    <t>The customer was experiencing a battery drain issue with their device, which started about a week ago. The agent provided troubleshooting steps, including restarting the device, checking for software updates, and resetting the device's settings. The customer was frustrated with the issue and requested that the agent look into the cause of the problem. The agent apologized for the inconvenience and offered to have the technical team investigate the issue.</t>
+  </si>
+  <si>
+    <t>I'm getting a bit frustrated</t>
+  </si>
+  <si>
+    <t>Customer is frustrated with the service, but the issue is being addressed and resolved, and the customer appreciates the agent's help.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon
+     AGENT
+     00:00:10
+     How can I assist you today?
+     CUSTOMER
+     00:00:15
+     I've been experiencing some issues with my internet connection. It's been slow and intermittent.
+     AGENT
+     00:00:22
+     Sorry to hear that. Can you tell me more about the issue? When did it start and have you noticed any patterns?
+     CUSTOMER
+     00:00:30
+     It started about a week ago. Sometimes it's fast, but most of the time it's slow. I've tried restarting my router, but it doesn't seem to make a difference.
+     AGENT
+     00:00:40
+     Okay, I'm going to go ahead and run some tests on our end to see if there are any outages or issues in your area. Can you please confirm your account information so I can look into this further?
+     CUSTOMER
+     00:00:50
+     Yeah, my account number is 123456.
+     AGENT
+     00:00:55
+     Thank you. I've checked on our end and it looks like there was a recent outage in your area that may have caused the issue. Our team is working to resolve it as soon as possible.
+     CUSTOMER
+     00:01:05
+     Okay, that's good to know. How long do you think it'll take to fix?
+     AGENT
+     00:01:10
+     We're estimating it should be resolved within the next 24-48 hours. In the meantime, I can offer you a temporary solution to help improve your internet speed.
+     CUSTOMER
+     00:01:20
+     That sounds good. What's the solution?
+     AGENT
+     00:01:25
+     We can provide you with a mobile hotspot device that will give you a more stable connection. Would you like me to set that up for you?
+     CUSTOMER
+     00:01:35
+     Yeah, that would be great. Thank you for your help.
+     AGENT
+     00:01:40
+     You're welcome. I'm going to go ahead and set up the mobile hotspot device for you. You should receive it within the next 3-5 business days. If you have any further issues, please don't hesitate to reach out to us.
+     CUSTOMER
+     00:01:50
+     Alright, thank you again.
+     AGENT
+     00:01:55
+     You're welcome. Have a great day."</t>
+  </si>
+  <si>
+    <t>The customer's tone is calm and factual throughout the conversation, without expressing any strong emotions such as happiness, frustration, or disappointment. They provide necessary information and ask questions to clarify the situation, indicating a neutral emotional state.</t>
+  </si>
+  <si>
+    <t>transcript61</t>
+  </si>
+  <si>
+    <t>Customer reported slow and intermittent internet connection. Agent ran tests and identified a recent outage in the customer's area. Temporary solution of a mobile hotspot device was offered to improve internet speed. Device will be set up and delivered within 3-5 business days.</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>The customer is calling about an issue with their internet connection, but the agent is able to resolve the issue and provide a temporary solution, and the customer is satisfied with the outcome.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon, I'm having some issues with your software. It's been freezing on me every time I try to open a new project.
+     AGENT
+     00:00:15
+     Sorry to hear that. Can you please tell me what version of the software you're currently using?
+     CUSTOMER
+     00:00:22
+     Yeah, I'm on the latest version. I just updated it last week.
+     AGENT
+     00:00:28
+     Okay, and have you tried restarting the software or your computer to see if that resolves the issue?
+     CUSTOMER
+     00:00:35
+     Of course, I've tried that. I'm not an idiot. But it still doesn't work.
+     AGENT
+     00:00:42
+     I apologize if my suggestion came across as condescending. That wasn't my intention. Let me see what else I can do to help you. Can you please provide me with more details about the error message you're seeing?
+     CUSTOMER
+     00:00:51
+     There is no error message. It just freezes. And I've already wasted an hour trying to troubleshoot it myself.
+     AGENT
+     00:01:00
+     I understand how frustrating that must be. I'm going to go ahead and escalate this issue to our advanced technical support team. They'll be able to assist you further.
+     CUSTOMER
+     00:01:08
+     Okay, thank you. I appreciate that.
+     AGENT
+     00:01:12
+     You're welcome. Someone from our team will reach out to you within the next 24 hours to assist you with the issue.
+     CUSTOMER
+     00:01:18
+     Alright, thank you.
+     AGENT
+     00:01:22
+     Is there anything else I can assist you with today?
+     CUSTOMER
+     00:01:27
+     No, that's it. Thanks again.
+     AGENT
+     00:01:31
+     You're welcome. Have a great day.
+     CUSTOMER
+     00:01:35
+     You too."</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration and annoyance throughout the conversation, particularly in their responses where they use strong language such as 'I'm not an idiot' and express frustration with the issue and the time wasted trying to troubleshoot it.</t>
+  </si>
+  <si>
+    <t>transcript62</t>
+  </si>
+  <si>
+    <t>Customer is experiencing issues with the software freezing when opening a new project. The customer has tried troubleshooting and is escalated to advanced technical support. A resolution is expected within 24 hours.</t>
+  </si>
+  <si>
+    <t>I'm not an idiot.</t>
+  </si>
+  <si>
+    <t>Customer tone is angry and frustrated with the service, indicating a medium churn risk.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon. I'm having some issues with my laptop's keyboard. Some of the keys are not working properly.
+     AGENT
+     00:00:15
+     Sorry to hear that. Can you please tell me more about the issue you're experiencing? Which keys are not working?
+     CUSTOMER
+     00:00:23
+     The 'e' and 't' keys are not registering when I press them. It's really frustrating because I need my laptop for work.
+     AGENT
+     00:00:32
+     I understand how frustrating that must be. Have you tried restarting your laptop or updating your keyboard drivers?
+     CUSTOMER
+     00:00:40
+     Yes, I've tried restarting and updating the drivers, but the problem persists. I'm not sure what else to do.
+     AGENT
+     00:00:48
+     Okay, let me see what else we can do. Can you please try pressing the 'e' and 't' keys while holding down the 'fn' key? Sometimes that can resolve the issue.
+     CUSTOMER
+     00:00:57
+     Okay, I'll try that. (pause) Nope, it didn't work.
+     AGENT
+     00:01:04
+     Alright, in that case, it's possible that there's a hardware issue with your keyboard. I'm going to go ahead and create a service request for you. We'll get someone to reach out to you to schedule a repair or replacement.
+     CUSTOMER
+     00:01:14
+     Okay, that sounds good. But how long is that going to take? I really need my laptop for work.
+     AGENT
+     00:01:21
+     I understand your concern. We'll do our best to expedite the process. You should receive a call from our service team within the next 24-48 hours to schedule a repair or replacement.
+     CUSTOMER
+     00:01:30
+     Okay, thank you. I appreciate your help.
+     AGENT
+     00:01:36
+     You're welcome. Is there anything else I can assist you with today?
+     CUSTOMER
+     00:01:42
+     No, that's all. Thank you again.
+     AGENT
+     00:01:47
+     You're welcome. Have a great day.
+     CUSTOMER
+     00:01:51
+     You too."</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration and annoyance throughout the conversation, particularly when describing the issue with their laptop's keyboard ('It's really frustrating because I need my laptop for work.') and when inquiring about the duration of the repair process ('But how long is that going to take? I really need my laptop for work.').</t>
+  </si>
+  <si>
+    <t>transcript63</t>
+  </si>
+  <si>
+    <t>Customer's laptop keyboard has issues with 'e' and 't' keys not registering. Agent tries troubleshooting steps, but the problem persists. A service request is created for a hardware issue, and the customer is scheduled for a repair or replacement within 24-48 hours.</t>
+  </si>
+  <si>
+    <t>it's really frustrating because I need my laptop for work</t>
+  </si>
+  <si>
+    <t>The customer is frustrated with the issue but the agent is able to resolve it and provide a solution, which reduces the churn risk to low.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon
+     AGENT
+     00:00:10
+     How can I assist you today?
+     CUSTOMER
+     00:00:15
+     I've been experiencing some issues with my internet connection. It's been slow and intermittent.
+     AGENT
+     00:00:22
+     Sorry to hear that. Can you tell me more about the issue? When did it start and have you noticed any patterns?
+     CUSTOMER
+     00:00:30
+     It started about a week ago. Sometimes it's fast, but most of the time it's slow. I've tried restarting my router, but it doesn't seem to make a difference.
+     AGENT
+     00:00:40
+     I see. Have you checked for any outages in your area? Sometimes that can cause intermittent performance.
+     CUSTOMER
+     00:00:47
+     Yeah, I checked the website and it says there are no outages. But I'm not sure if that's accurate.
+     AGENT
+     00:00:55
+     Okay. I'm going to go ahead and run some tests on your connection. Can you please confirm your account information so I can access your account?
+     CUSTOMER
+     00:01:02
+     Yeah, it's *** *** ***.
+     AGENT
+     00:01:10
+     Okay, thank you. I'm running the tests now. (pause) Okay, it looks like there may be an issue with your modem. I'm going to go ahead and send a signal to it to see if that resolves the issue.
+     CUSTOMER
+     00:01:25
+     Okay, that sounds good. But what if it doesn't work? I'm getting really frustrated with this.
+     AGENT
+     00:01:32
+     I completely understand. If the signal doesn't work, we can discuss further troubleshooting steps or potentially schedule a technician to visit your location to resolve the issue.
+     CUSTOMER
+     00:01:40
+     Okay, that sounds good. Thank you for your help.
+     AGENT
+     00:01:45
+     You're welcome. I'm going to go ahead and send the signal now. If you have any further issues, please don't hesitate to reach out to us.
+     CUSTOMER
+     00:01:50
+     Alright, thank you.
+     AGENT
+     00:01:55
+     You're welcome. Have a great day.
+     CUSTOMER
+     00:02:00
+     You too.
+     "</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration and annoyance with the issue they're experiencing, stating 'I'm getting really frustrated with this.' This indicates a strong negative emotion, which is characteristic of anger.</t>
+  </si>
+  <si>
+    <t>transcript64</t>
+  </si>
+  <si>
+    <t>Customer reported slow and intermittent internet connection. Agent ran tests and suspected modem issue. Sent signal to modem to resolve issue. Discussed further troubleshooting steps if necessary.</t>
+  </si>
+  <si>
+    <t>I'm getting really frustrated with this</t>
+  </si>
+  <si>
+    <t>The customer is frustrated with the internet connection issue, but the agent is actively trying to resolve the issue and the customer's tone changes to a more positive one after the agent's solution.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon. I'm having some trouble with my internet connection. The audio quality is really poor and it's affecting my online meetings.
+     AGENT
+     00:00:15
+     Sorry to hear that. Can you please tell me more about the issue you're experiencing? What kind of poor audio quality are you experiencing?
+     CUSTOMER
+     00:00:25
+     Well, there's a lot of static and crackling. It's really frustrating because I need a reliable connection for my work.
+     AGENT
+     00:00:35
+     I understand. Have you tried restarting your router or modem to see if that resolves the issue?
+     CUSTOMER
+     00:00:43
+     Yeah, I've tried that already. It doesn't seem to make a difference.
+     AGENT
+     00:00:50
+     Okay. In that case, I'd like to run some diagnostic tests to see if we can identify the root cause of the problem. Can you please confirm your account information so I can access your account?
+     CUSTOMER
+     00:01:00
+     Yeah, it's *** *** ***.
+     AGENT
+     00:01:05
+     Thank you. I'm going to go ahead and run those tests. Can you please hold for just a minute?
+     CUSTOMER
+     00:01:12
+     Okay...
+     AGENT
+     00:01:25
+     Okay, I've run the tests and it looks like there may be an issue with your connection speed. I'm going to go ahead and escalate this issue to our advanced technical support team. They'll be able to assist you further.
+     CUSTOMER
+     00:01:40
+     Okay, thank you. I appreciate your help.
+     AGENT
+     00:01:45
+     You're welcome. I apologize again for the inconvenience and appreciate your patience. Is there anything else I can assist you with today?
+     CUSTOMER
+     00:01:50
+     No, that's all. Thanks again.
+     AGENT
+     00:01:55
+     You're welcome. Have a great day.
+     CUSTOMER
+     00:02:00
+     You too."</t>
+  </si>
+  <si>
+    <t>The customer's tone is calm and factual throughout the conversation, with a focus on describing the issue and seeking a resolution. Although they express frustration with the poor audio quality, their language remains objective and polite, without any strong emotional undertones.</t>
+  </si>
+  <si>
+    <t>transcript65</t>
+  </si>
+  <si>
+    <t>Customer experiencing poor audio quality due to static and crackling, escalated to advanced technical support team for further assistance.</t>
+  </si>
+  <si>
+    <t>The customer is frustrated with the internet connection issue, but the agent is able to assist and resolve the issue, which reduces the churn risk to low.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon. I'm having some trouble setting up my new device. I've tried following the instructions but it's not working.
+     AGENT
+     00:00:15
+     Sorry to hear that. Can you please tell me more about the issue you're experiencing? What kind of device are you trying to set up?
+     CUSTOMER
+     00:00:25
+     It's a smart TV. I've tried connecting it to my Wi-Fi network but it's not recognizing the network.
+     AGENT
+     00:00:35
+     Okay. Let's try to troubleshoot the issue. Have you checked if your Wi-Fi network name and password are correct?
+     CUSTOMER
+     00:00:45
+     Yes, I've double-checked and they're correct. I've even tried restarting the router but that didn't work either.
+     AGENT
+     00:00:55
+     Okay. In that case, let's try resetting the TV's network settings. Can you please go to the TV's settings menu and select 'Network' and then 'Reset Network Settings'?
+     CUSTOMER
+     00:01:05
+     Okay, I've done that. But it's still not working.
+     AGENT
+     00:01:15
+     Okay. Let's try one more thing. Can you please try connecting the TV to your router using an Ethernet cable instead of Wi-Fi?
+     CUSTOMER
+     00:01:25
+     Okay, I'll try that. But I'm getting a bit frustrated with this process. I've been trying to set this up for hours.
+     AGENT
+     00:01:35
+     I completely understand. I apologize for the inconvenience. If the Ethernet cable doesn't work, we may need to escalate this issue to our advanced technical support team. But let's try the Ethernet cable first and see if that resolves the issue.
+     CUSTOMER
+     00:01:45
+     Okay, fine. I'll try that.
+     AGENT
+     00:01:55
+     Great. And if you're still having trouble, I'll go ahead and escalate the issue to our advanced technical support team. They'll be able to assist you further.
+     CUSTOMER
+     00:02:05
+     Okay, thank you. I appreciate your help.
+     AGENT
+     00:02:15
+     You're welcome. I'm sorry again for the trouble you're experiencing. We'll get this resolved for you as soon as possible.
+     "</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration and annoyance throughout the conversation, particularly in the message 'I've been trying to set this up for hours' and 'I'm getting a bit frustrated with this process'. The customer's tone is clear and direct, indicating a strong negative emotion.</t>
+  </si>
+  <si>
+    <t>transcript66</t>
+  </si>
+  <si>
+    <t>Customer is having trouble setting up a smart TV, experiencing issues with Wi-Fi connection. Agent provides troubleshooting steps, including resetting network settings and using an Ethernet cable. If issue persists, agent will escalate to advanced technical support team.</t>
+  </si>
+  <si>
+    <t>I'm getting a bit frustrated with this process.</t>
+  </si>
+  <si>
+    <t>The customer is frustrated with the setup process, but the agent is actively trying to resolve the issue and the customer is still willing to try the suggested solutions.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon
+     AGENT
+     00:00:10
+     How can I assist you today?
+     CUSTOMER
+     00:00:15
+     I'm having some issues with my laptop's keyboard. Some keys are not working properly.
+     AGENT
+     00:00:22
+     Sorry to hear that. Can you tell me more about the issue? Which keys are not working?
+     CUSTOMER
+     00:00:30
+     The 'e' and 't' keys are not registering when I press them. It's really frustrating.
+     AGENT
+     00:00:37
+     I understand. Have you tried cleaning the keyboard or checking for any debris that might be causing the issue?
+     CUSTOMER
+     00:00:44
+     Yeah, I've tried cleaning it, but it didn't make a difference.
+     AGENT
+     00:00:50
+     Okay. In that case, it's possible that there's a hardware issue with the keyboard. I'm going to go ahead and troubleshoot some more with you. Can you try pressing the 'e' and 't' keys simultaneously and see if they register then?
+     CUSTOMER
+     00:01:00
+     Okay... yeah, they're still not working.
+     AGENT
+     00:01:05
+     Alright. I'm going to go ahead and escalate this issue to our advanced technical support team. They'll be able to assist you further with the hardware issue. Is that okay with you?
+     CUSTOMER
+     00:01:12
+     Yeah, that sounds good. Thank you.
+     AGENT
+     00:01:15
+     You're welcome. I'll go ahead and escalate the issue. You should receive an email with a case number and further instructions within the next 30 minutes.
+     CUSTOMER
+     00:01:22
+     Alright, thank you again for your help.
+     AGENT
+     00:01:25
+     You're welcome. Have a great day!"</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration and annoyance with the issue they're experiencing ('It's really frustrating'). They also use a slightly aggressive tone when describing the problem ('The 'e' and 't' keys are not registering when I press them').</t>
+  </si>
+  <si>
+    <t>transcript67</t>
+  </si>
+  <si>
+    <t>Customer is experiencing issues with their laptop's keyboard, specifically the 'e' and 't' keys not registering. Agent troubleshoots the issue, determines it may be a hardware problem, and escalates it to advanced technical support for further assistance.</t>
+  </si>
+  <si>
+    <t>It's really frustrating</t>
+  </si>
+  <si>
+    <t>The customer is frustrated with the issue, but the agent is able to assist and provide a solution, which reduces the risk of churn.</t>
+  </si>
+  <si>
+    <t>"AGENT
+00:00:00
+Hello good afternoon.
+CUSTOMER
+00:00:07
+good afternoon. I'm having some issues with my phone's battery. It's been draining really fast lately.
+AGENT
+00:00:15
+Sorry to hear that. Can you tell me more about the issue you're experiencing? How long has this been going on?
+CUSTOMER
+00:00:25
+It started about a week ago. I've tried closing some apps, turning off location services, and even turning down the screen brightness, but nothing seems to be working.
+AGENT
+00:00:40
+I see. Have you tried calibrating your battery or doing a factory reset?
+CUSTOMER
+00:00:50
+Yeah, I've tried calibrating it, but it didn't make a difference. And I don't want to do a factory reset because I'll lose all my data.
+AGENT
+00:01:00
+I understand your concern. Let me see what else we can do. Can you tell me what kind of phone you have and what's your current battery health?
+CUSTOMER
+00:01:10
+I have an iPhone 12, and according to the settings, my battery health is at 80%.
+AGENT
+00:01:20
+Okay. In that case, it's possible that the battery is just naturally degrading. But I want to try a few more things before we consider replacing the battery. Can you try turning off background app refresh and see if that makes a difference?
+CUSTOMER
+00:01:35
+I've already tried that. Like I said, I've tried everything I can think of. I'm really frustrated with this phone. I've only had it for a year and it's already giving me problems.
+AGENT
+00:01:50
+I understand why you're frustrated. Let me see what else we can do. Can you please hold for just a minute while I check on some options for you?
+CUSTOMER
+00:02:00
+(sighs) Fine.
+AGENT
+00:02:10
+Okay, I've checked on some options. It looks like we can offer you a replacement battery for a discounted price. Would you like to take advantage of that offer?
+CUSTOMER
+00:02:25
+How much is it going to cost me?
+AGENT
+00:02:35
+The replacement battery would be $50.
+CUSTOMER
+00:02:45
+That's still a lot of money. I don't know if I want to spend that much on a phone that's only a year old.
+AGENT
+00:03:00
+I understand your concern. Let me see what else I can do. (pauses) Okay, I can offer you a $10 discount on the replacement battery. Would you like to take advantage of that offer?
+CUSTOMER
+00:03:20
+(sighs) I guess so. But I'm still not happy about this.
+AGENT
+00:03:30
+I understand, and I apologize again for the inconvenience. I'm going to go ahead and process the order for the replacement battery. You should receive it within 3-5 business days.
+CUSTOMER
+00:03:45
+Okay. Thanks, I guess.
+AGENT
+00:03:50
+You're welcome. Is there anything else I can assist you with today?
+CUSTOMER
+00:04:00
+No, that's it. Thanks.
+AGENT
+00:04:05
+You're welcome. Have a good day.
+CUSTOMER
+00:04:10
+You too.</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration and annoyance throughout the conversation, particularly when discussing the issue with their phone's battery and the cost of the replacement battery. They use phrases like 'I'm really frustrated with this phone' and 'I'm still not happy about this,' indicating a strong negative emotion.</t>
+  </si>
+  <si>
+    <t>transcript68</t>
+  </si>
+  <si>
+    <t>The customer is experiencing a fast-draining battery issue with their iPhone 12, which started about a week ago. They have tried various troubleshooting steps, including closing apps, turning off location services, and calibrating the battery, but nothing has worked. The agent offers a replacement battery for a discounted price of $50, which is later reduced to $40 after a $10 discount. The customer agrees to the offer and the agent processes the order.</t>
+  </si>
+  <si>
+    <t>I'm really frustrated with this phone.</t>
+  </si>
+  <si>
+    <t>The customer is frustrated with their phone's battery issue, but the agent is able to offer a solution and the customer agrees to it, showing some minor dissatisfaction.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon
+     AGENT
+     00:00:10
+     Hi Joy, thank you for reaching out to us. My name is Alex, and I'll be happy to assist you with your concern. Can you please tell me a little bit about what's going on?
+     CUSTOMER
+     00:00:20
+     Yeah, I'm having some issues with my phone. I dropped it and the screen is cracked. I'm not sure if it's still under warranty.
+     AGENT
+     00:00:30
+     Sorry to hear that, Joy. Can you please provide me with your phone's serial number or the order number so I can look into this further for you?
+     CUSTOMER
+     00:00:40
+     Yeah, it's #123456789.
+     AGENT
+     00:00:50
+     Thank you, Joy. I've located your order. It looks like your phone is still under warranty. We can definitely help you with the repair or replacement of your phone.
+     CUSTOMER
+     00:01:00
+     That's great news! What's the process for getting it fixed?
+     AGENT
+     00:01:10
+     We can either repair your phone or replace it with a new one, whichever you prefer. If you'd like to proceed with the repair, we can send you a prepaid return shipping label and get it fixed for you.
+     CUSTOMER
+     00:01:20
+     That sounds good. How long will it take to get it back?
+     AGENT
+     00:01:30
+     The repair process usually takes around 5-7 business days. We'll also provide you with a loaner phone in the meantime so you're not without a phone.
+     CUSTOMER
+     00:01:40
+     Okay, that sounds like a plan. What do I need to do next?
+     AGENT
+     00:01:50
+     I'll go ahead and send you the prepaid return shipping label via email. Just print it out, package your phone securely, and drop it off at any UPS location. We'll take care of the rest.
+     CUSTOMER
+     00:02:00
+     Alright, got it. Thanks so much for your help, Alex.
+     AGENT
+     00:02:10
+     You're welcome, Joy. It was my pleasure to assist you. If you have any other questions or concerns, don't hesitate to reach out to us. Have a great day!
+     CUSTOMER
+     00:02:20
+     You too, thanks again."</t>
+  </si>
+  <si>
+    <t>8.5</t>
+  </si>
+  <si>
+    <t>The customer expresses happiness and satisfaction throughout the conversation, especially when receiving positive news about their warranty and the repair process. They also use phrases like 'That's great news!' and 'Thanks so much for your help', indicating a positive tone.</t>
+  </si>
+  <si>
+    <t>transcript69</t>
+  </si>
+  <si>
+    <t>The customer, Joy, had issues with her phone due to a cracked screen after dropping it. Alex, the agent, assisted her in checking the warranty and offered repair or replacement options. The process involved sending a prepaid return shipping label, providing a loaner phone, and taking around 5-7 business days to complete the repair.</t>
+  </si>
+  <si>
+    <t>The customer is calling to inquire about repairing their cracked phone screen, and the agent is able to assist them with the process. The tone of the conversation is polite and helpful, with no indication of frustration or dissatisfaction that would suggest churn.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon. I'm having some issues with my computer. The audio output isn't working.
+     AGENT
+     00:00:15
+     Sorry to hear that. Can you tell me more about the issue you're experiencing? When did it start happening?
+     CUSTOMER
+     00:00:25
+     It started yesterday. I was watching a video and suddenly the sound just stopped. I've tried restarting my computer and updating my drivers, but nothing's working.
+     AGENT
+     00:00:40
+     Okay, let's try to troubleshoot the issue. Have you checked if the audio output is set to the correct device?
+     CUSTOMER
+     00:00:50
+     Yes, I've checked that. It's set to the correct device. I've also tried using a different set of speakers, but that didn't work either.
+     AGENT
+     00:01:05
+     Okay. In that case, let's try to run a diagnostic test on your audio system. Can you please follow these steps...?
+     CUSTOMER
+     00:01:15
+     (angrily) Look, I've already tried all that. I just want to know when you're going to fix the problem. I've been on hold for 20 minutes and I'm getting frustrated.
+     AGENT
+     00:01:25
+     I apologize for the inconvenience. I understand how frustrating it can be. Let me see what I can do to expedite the process. Can you please hold for just another minute?
+     CUSTOMER
+     00:01:40
+     (sighs) Fine.
+     AGENT
+     00:01:50
+     Okay, I've escalated the issue to our advanced technical support team. They'll be able to assist you further. Someone will be calling you within the next 24 hours.
+     CUSTOMER
+     00:02:05
+     (angrily) 24 hours? That's unacceptable. I need this fixed now.
+     AGENT
+     00:02:15
+     I understand your concern, but I assure you that our team will do their best to resolve the issue as soon as possible. In the meantime, I can offer you a complimentary... 
+     CUSTOMER
+     00:02:30
+     (interrupting) No, I don't want any complimentary services. I just want my audio output fixed.
+     AGENT
+     00:02:40
+     I understand. I'll make sure to follow up on your issue and ensure that it's resolved as soon as possible. Is there anything else I can assist you with today?
+     CUSTOMER
+     00:02:50
+     (angrily) No, that's it. Just fix my audio output.
+     AGENT
+     00:03:00
+     Okay, I'll make sure to do that. Thank you for your patience and understanding. Have a good day.
+     CUSTOMER
+     00:03:05
+     (angrily) Yeah, right. Good day."</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration, annoyance, and strong dissatisfaction throughout the conversation, particularly when discussing the issue's duration and the proposed solution's timeline.</t>
+  </si>
+  <si>
+    <t>transcript70</t>
+  </si>
+  <si>
+    <t>Customer experiences audio output issues, agent apologizes and escalates to advanced technical support for resolution within 24 hours.</t>
+  </si>
+  <si>
+    <t>I've been on hold for 20 minutes and I'm getting frustrated</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon, I'm having some issues with the software. It's been freezing on me all morning.
+     AGENT
+     00:00:15
+     Sorry to hear that. Can you please tell me more about the issue you're experiencing? What were you doing when it started freezing?
+     CUSTOMER
+     00:00:25
+     I was trying to upload a file, and then it just stopped working. I've tried restarting the program, but it still doesn't work.
+     AGENT
+     00:00:35
+     Okay, let me see what I can do to help you. Can you please confirm the version of the software you're using?
+     CUSTOMER
+     00:00:43
+     Yeah, it's the latest version. I just updated it last week.
+     AGENT
+     00:00:50
+     Alright. In that case, I'm going to go ahead and remote access your computer to take a closer look. Is that okay with you?
+     CUSTOMER
+     00:00:58
+     Yeah, that's fine. But I'm getting a bit frustrated because I really need to get this work done today.
+     AGENT
+     00:01:05
+     I completely understand, and I apologize again for the inconvenience. I'll do my best to get this resolved as quickly as possible.
+     CUSTOMER
+     00:01:12
+     Okay, thanks. I appreciate it.
+     AGENT
+     00:01:20
+     Okay, I'm in now. Let me just take a look... (pause) Okay, I think I see the problem. It looks like there's a conflict with another program you have installed.
+     CUSTOMER
+     00:01:35
+     Oh, really? Which one?
+     AGENT
+     00:01:40
+     It looks like it's conflicting with your antivirus software. I can walk you through how to resolve the issue if you'd like.
+     CUSTOMER
+     00:01:48
+     Yeah, please do. I don't have time to deal with this anymore.
+     AGENT
+     00:01:55
+     Okay, no problem. Just follow my instructions, and we should be able to get this resolved. First, can you please disable your antivirus software?
+     CUSTOMER
+     00:02:03
+     Okay, done.
+     AGENT
+     00:02:08
+     Great. Now, let's try uploading the file again. Is it working now?
+     CUSTOMER
+     00:02:15
+     Yeah, it's working now. Thanks so much for your help.
+     AGENT
+     00:02:20
+     You're welcome. I'm glad I could assist you. If you have any other issues, don't hesitate to reach out. Have a great day.
+     CUSTOMER
+     00:02:25
+     You too. Thanks again.
+     "</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration and annoyance throughout the conversation, particularly when they mention 'I'm getting a bit frustrated because I really need to get this work done today' and 'I don't have time to deal with this anymore'. Their tone is also somewhat aggressive when they ask 'Which one?' in response to the agent's suggestion of a conflict with another program.</t>
+  </si>
+  <si>
+    <t>transcript71</t>
+  </si>
+  <si>
+    <t>The customer was experiencing issues with the software freezing on them while trying to upload a file. The agent remote accessed the customer's computer, identified the issue as a conflict with the antivirus software, and walked the customer through the steps to resolve the issue, which successfully resolved the problem.</t>
+  </si>
+  <si>
+    <t>The customer is frustrated with the service, but the issue is resolved, and the tone changes to appreciation.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon
+     AGENT
+     00:00:10
+     Thank you for reaching out to us. How can I assist you today?
+     CUSTOMER
+     00:00:15
+     Hi, I'm having some issues with my computer. The audio isn't working.
+     AGENT
+     00:00:20
+     Sorry to hear that. Can you tell me more about the issue you're experiencing? When did it start?
+     CUSTOMER
+     00:00:25
+     It started yesterday. I was watching a video and suddenly the audio just stopped working.
+     AGENT
+     00:00:30
+     Okay. Have you tried restarting your computer or checking the audio settings?
+     CUSTOMER
+     00:00:35
+     Yeah, I've tried restarting and checking the settings, but nothing seems to work.
+     AGENT
+     00:00:40
+     Alright. Let's try to troubleshoot this further. Can you please check if the audio cable is securely plugged in?
+     CUSTOMER
+     00:00:45
+     Yeah, it's plugged in securely.
+     AGENT
+     00:00:50
+     Okay. In that case, it's possible that the issue is with the audio driver. I can walk you through the steps to update the driver.
+     CUSTOMER
+     00:00:55
+     Okay, that sounds good.
+     AGENT
+     00:01:00
+     Great. First, you'll need to go to the device manager and find the audio device. Then, you'll need to right-click on it and select 'update driver'.
+     CUSTOMER
+     00:01:05
+     Okay, got it.
+     AGENT
+     00:01:10
+     Once you've updated the driver, restart your computer and see if the audio is working again.
+     CUSTOMER
+     00:01:15
+     Alright, I'll try that. Thanks for your help.
+     AGENT
+     00:01:20
+     You're welcome. If you have any more issues or need further assistance, don't hesitate to reach out to us. Have a great day!"</t>
+  </si>
+  <si>
+    <t>The customer's language and tone throughout the conversation are calm and factual, indicating a neutral emotional state. They report their issue, provide necessary information, and follow the agent's instructions without expressing any strong emotions such as frustration, disappointment, or happiness.</t>
+  </si>
+  <si>
+    <t>transcript72</t>
+  </si>
+  <si>
+    <t>Customer reported audio issues with their computer, which started yesterday while watching a video. Agent assisted in troubleshooting, suggesting restarting the computer, checking audio settings, and updating the audio driver. Customer agreed to try updating the driver and restarting the computer to resolve the issue.</t>
+  </si>
+  <si>
+    <t>The customer is calling about a technical issue with their computer, and the agent is able to assist them in resolving the issue. There is no indication of churn or dissatisfaction with the company.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon. I'm having some trouble setting up my new device. I'm not sure what I'm doing wrong.
+     AGENT
+     00:00:15
+     Sorry to hear that you're having trouble setting up your device. Can you please tell me more about the issue you're experiencing? What kind of device are you trying to set up?
+     CUSTOMER
+     00:00:27
+     It's a smart TV. I'm trying to connect it to my Wi-Fi network, but it's not recognizing the network.
+     AGENT
+     00:00:37
+     Okay, let's try to troubleshoot the issue. Have you checked to make sure your Wi-Fi network name and password are correct?
+     CUSTOMER
+     00:00:45
+     Yes, I've double-checked them. I'm positive they're correct.
+     AGENT
+     00:00:53
+     Alright. In that case, let's try restarting your router and TV. Sometimes, a simple reboot can resolve connectivity issues.
+     CUSTOMER
+     00:01:03
+     Okay, I'll try that. But I'm getting a bit frustrated. I've been trying to set this up for hours.
+     AGENT
+     00:01:11
+     I completely understand your frustration. I'm here to help you resolve the issue as quickly as possible. If restarting the router and TV doesn't work, we can try some other troubleshooting steps.
+     CUSTOMER
+     00:01:22
+     Okay, I've restarted them. But it's still not working.
+     AGENT
+     00:01:30
+     Okay. Let's try changing the Wi-Fi channel on your router. Sometimes, interference from other devices can cause connectivity issues.
+     CUSTOMER
+     00:01:40
+     How do I do that?
+     AGENT
+     00:01:47
+     You can usually find the Wi-Fi channel settings in your router's configuration page. I can walk you through the steps if you'd like.
+     CUSTOMER
+     00:01:55
+     Yeah, that would be great. I'm not very tech-savvy.
+     AGENT
+     00:02:02
+     No problem at all. I'm here to help. Let me guide you through the process.
+     CUSTOMER
+     00:02:10
+     Okay, I think I've changed the channel. But it's still not working.
+     AGENT
+     00:02:18
+     Okay. In that case, I'm going to go ahead and escalate this issue to our advanced technical support team. They'll be able to assist you further.
+     CUSTOMER
+     00:02:27
+     Okay, thank you. I appreciate your help.
+     AGENT
+     00:02:34
+     You're welcome. I apologize again for the inconvenience you've experienced. We'll get this resolved for you as soon as possible."</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration and annoyance throughout the conversation, particularly when they mention 'I've been trying to set this up for hours' and 'I'm not very tech-savvy'. Their tone suggests they are upset and seeking help to resolve the issue.</t>
+  </si>
+  <si>
+    <t>transcript73</t>
+  </si>
+  <si>
+    <t>Customer had trouble setting up a smart TV, specifically connecting it to their Wi-Fi network. Agent provided troubleshooting steps, including restarting the router and TV, changing the Wi-Fi channel, and escalating the issue to advanced technical support. Customer appreciated the agent's help and assistance.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon. I'm having some issues with my internet connection. It's been slow and dropping out frequently.
+     AGENT
+     00:00:15
+     Sorry to hear that. Can you please tell me more about the issue you're experiencing? What's your internet speed like?
+     CUSTOMER
+     00:00:25
+     It's been really slow. I've tried restarting my router but it doesn't seem to make a difference. And sometimes it just drops out completely.
+     AGENT
+     00:00:35
+     Okay, I see. Have you tried checking for any outages in your area?
+     CUSTOMER
+     00:00:42
+     Yeah, I've checked the website and there aren't any outages reported.
+     AGENT
+     00:00:50
+     Alright. In that case, I'd like to try and troubleshoot the issue further. Can you please check the cables and make sure they're securely connected?
+     CUSTOMER
+     00:01:00
+     Yeah, I've already checked that. Like I said, I've tried restarting the router too.
+     AGENT
+     00:01:08
+     Okay, no worries. Let me check on our end to see if there are any issues with your account. Can you please provide me with your account ID?
+     CUSTOMER
+     00:01:18
+     It's 123456.
+     AGENT
+     00:01:25
+     Thank you. I've checked on our end and it looks like there's an issue with your connection. I'm going to go ahead and send a signal to your router to try and resolve the issue.
+     CUSTOMER
+     00:01:40
+     Okay, how long will that take?
+     AGENT
+     00:01:45
+     It should only take a few minutes. You might experience a brief outage while the signal is being sent.
+     CUSTOMER
+     00:01:55
+     Alright, I'll wait.
+     AGENT
+     00:02:10
+     Okay, the signal has been sent. Can you please try checking your internet connection again?
+     CUSTOMER
+     00:02:20
+     Yeah, it seems to be working now. Thanks for your help.
+     AGENT
+     00:02:25
+     You're welcome! I'm glad we could resolve the issue. If you experience any further problems, don't hesitate to reach out to us.
+     CUSTOMER
+     00:02:30
+     Will do, thanks again.
+     AGENT
+     00:02:35
+     You're welcome. Have a great day!
+     CUSTOMER
+     00:02:40
+     You too."</t>
+  </si>
+  <si>
+    <t>The customer's tone is calm and factual throughout the conversation, with a focus on describing the issue and seeking resolution. They express frustration and disappointment with the slow internet connection, but their language remains neutral and objective.</t>
+  </si>
+  <si>
+    <t>transcript74</t>
+  </si>
+  <si>
+    <t>Customer reported slow and dropping internet connection. Agent helped troubleshoot the issue, checked for outages, and sent a signal to the customer's router to resolve the problem. The issue was resolved, and the customer's internet connection was restored.</t>
+  </si>
+  <si>
+    <t>The customer is calling about a specific issue with their internet connection, and the agent is able to resolve the issue. The customer's tone is not angry or frustrated, and there is no mention of switching companies.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon. I'm calling because I'm having some issues with my internet connection. It's been slow and intermittent all day.
+     AGENT
+     00:00:15
+     Sorry to hear that. Can you tell me a little bit more about what's been going on? When did you first notice the issue?
+     CUSTOMER
+     00:00:23
+     It started this morning. I was trying to work from home and I couldn't even load a webpage. It's been on and off all day.
+     AGENT
+     00:00:31
+     Okay, I'm going to go ahead and check on the status of our network in your area. Can you please confirm your account information so I can look into this further?
+     CUSTOMER
+     00:00:39
+     Yeah, my account number is 123456.
+     AGENT
+     00:00:45
+     Thank you. I'm showing that there are no outages in your area, but I do see that your modem is not functioning properly. I'm going to go ahead and send a signal to your modem to try and reset it.
+     CUSTOMER
+     00:00:54
+     Okay, that sounds good. But I've already tried restarting it myself and it didn't work.
+     AGENT
+     00:01:01
+     I understand. In that case, I'm going to go ahead and schedule a technician to come out to your location to take a closer look. Would you be available tomorrow or Wednesday?
+     CUSTOMER
+     00:01:09
+     Tomorrow is fine. But I'm really frustrated that I've had to deal with this all day. I expect better service from your company.
+     AGENT
+     00:01:17
+     I completely understand, and I apologize for the inconvenience. I'm going to go ahead and credit your account for the trouble you've experienced today.
+     CUSTOMER
+     00:01:24
+     Okay, thank you. I appreciate that.
+     AGENT
+     00:01:29
+     You're welcome. Is there anything else I can assist you with today?
+     CUSTOMER
+     00:01:34
+     No, that's all. Thank you.
+     AGENT
+     00:01:38
+     You're welcome. Have a great day.
+     CUSTOMER
+     00:01:41
+     You too.
+     "</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration and disappointment with the service they received, stating 'I'm really frustrated that I've had to deal with this all day' and 'I expect better service from your company'. This indicates a strong negative emotion, which is characteristic of anger.</t>
+  </si>
+  <si>
+    <t>transcript75</t>
+  </si>
+  <si>
+    <t>Customer reported slow and intermittent internet connection. Agent checked network status and found modem not functioning properly. Technician scheduled to visit customer's location to investigate further. Customer credited for inconvenience.</t>
+  </si>
+  <si>
+    <t>I expect better service from your company.</t>
+  </si>
+  <si>
+    <t>The customer is frustrated with the service and has had to deal with the issue all day, showing a tone of anger and frustration.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon
+     AGENT
+     00:00:10
+     I'm so sorry to hear that you're experiencing poor audio quality. Can you tell me more about the issue you're facing?
+     CUSTOMER
+     00:00:17
+     yeah... I'm having trouble hearing the other person on the call. It's all static and fuzzy.
+     AGENT
+     00:00:24
+     I apologize for the inconvenience. Have you tried restarting your device or checking your internet connection?
+     CUSTOMER
+     00:00:31
+     yeah... I've tried that already. It didn't make a difference.
+     AGENT
+     00:00:36
+     Okay. In that case, I'd like to troubleshoot the issue further. Can you please tell me what type of device you're using and what browser or app you're on?
+     CUSTOMER
+     00:00:43
+     I'm using my laptop and the chrome browser.
+     AGENT
+     00:00:48
+     Alright. I'm going to go ahead and check on our end to see if there are any outages or issues that might be causing the problem. Can you please hold for just a minute?
+     CUSTOMER
+     00:00:55
+     okay...
+     AGENT
+     00:01:02
+     Okay, I've checked and it looks like there might be an issue with our servers. I'm going to go ahead and escalate this to our technical team to get it resolved as soon as possible.
+     CUSTOMER
+     00:01:10
+     okay... thank you.
+     AGENT
+     00:01:13
+     You're welcome. I apologize again for the inconvenience and appreciate your patience. We'll get this resolved for you as soon as possible.
+     CUSTOMER
+     00:01:19
+     yeah... thanks.
+     AGENT
+     00:01:22
+     Is there anything else I can assist you with in the meantime?
+     CUSTOMER
+     00:01:26
+     no... that's it.
+     AGENT
+     00:01:29
+     Alright. Well, I'll go ahead and follow up with you once the issue is resolved. Thank you for reaching out to us and I hope you have a better day.
+     CUSTOMER
+     00:01:36
+     yeah... you too.
+     "</t>
+  </si>
+  <si>
+    <t>The customer's language and tone throughout the conversation are calm and factual, without expressing any strong emotions such as happiness, frustration, or disappointment. They seem to be patiently waiting for a resolution to their issue, which suggests a neutral emotional state.</t>
+  </si>
+  <si>
+    <t>transcript76</t>
+  </si>
+  <si>
+    <t>The customer experienced poor audio quality on a call, which was attributed to an issue with the company's servers. The agent apologized for the inconvenience, offered troubleshooting steps, and escalated the issue to the technical team for resolution.</t>
+  </si>
+  <si>
+    <t>The customer is frustrated with the poor audio quality, but the agent is apologetic and helpful, and the issue is being escalated to the technical team. The customer's tone is minorly dissatisfied, but there is no explicit or implicit mention of churn.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon. I'm having some issues with my account. I've been trying to access my dashboard but it keeps saying my password is incorrect.
+     AGENT
+     00:00:15
+     Sorry to hear that you're experiencing some trouble. Can you please try resetting your password and see if that resolves the issue?
+     CUSTOMER
+     00:00:25
+     I've already tried that. It didn't work. I'm getting really frustrated with this.
+     AGENT
+     00:00:32
+     I apologize for the inconvenience. Let me see what else I can do to help. Can you please confirm your username so I can look into this further?
+     CUSTOMER
+     00:00:40
+     It's johndoe123.
+     AGENT
+     00:00:47
+     Okay, thank you. I'm going to go ahead and reset your password for you. You should receive an email with a new temporary password shortly.
+     CUSTOMER
+     00:00:55
+     Okay... I hope this works. I've been having a lot of issues with your service lately.
+     AGENT
+     00:01:02
+     I apologize again for the trouble. I'm going to go ahead and escalate this issue to our advanced technical support team. They'll be able to take a closer look and make sure everything is resolved.
+     CUSTOMER
+     00:01:10
+     Okay... thanks, I guess.
+     AGENT
+     00:01:15
+     You're welcome. Is there anything else I can assist you with today?
+     CUSTOMER
+     00:01:20
+     No... I just want to get this fixed.
+     AGENT
+     00:01:25
+     I completely understand. I'm going to go ahead and follow up with you in 24 hours to make sure everything is resolved to your satisfaction.
+     CUSTOMER
+     00:01:32
+     Okay... thanks.
+     AGENT
+     00:01:37
+     You're welcome. Is there anything else you'd like to add or any other concerns you have?
+     CUSTOMER
+     00:01:43
+     No... that's it.
+     AGENT
+     00:01:47
+     Alright. Thank you for bringing this to my attention. I'll make sure to get everything resolved for you.
+     CUSTOMER
+     00:01:52
+     Thanks.
+     AGENT
+     00:01:55
+     You're welcome. Have a great day.
+     CUSTOMER
+     00:01:58
+     Yeah... you too."</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration and annoyance throughout the conversation, using phrases such as 'I'm getting really frustrated with this' and 'I've been having a lot of issues with your service lately'. The customer's tone is also negative, with a focus on resolving the issue rather than expressing gratitude or satisfaction.</t>
+  </si>
+  <si>
+    <t>transcript77</t>
+  </si>
+  <si>
+    <t>Customer had issues accessing their account dashboard due to incorrect password. Agent assisted in resetting password, escalating the issue to advanced technical support, and following up with the customer to ensure resolution.</t>
+  </si>
+  <si>
+    <t>I've been having a lot of issues with your service lately</t>
+  </si>
+  <si>
+    <t>Customer is frustrated with the service and has been having issues, but there is no explicit or implicit mention of switching companies.</t>
+  </si>
+  <si>
+    <t>"AGENT
+       00:00:00
+       Hello good afternoon.
+       CUSTOMER
+       00:00:07
+       good afternoon. I'm having some issues with my phone's battery. It's been draining really fast lately.
+       AGENT
+       00:00:15
+       Sorry to hear that. Can you tell me more about the issue? How long has this been happening?
+       CUSTOMER
+       00:00:25
+       It started about a week ago. I've tried closing some apps and turning off location services, but nothing seems to be working.
+       AGENT
+       00:00:35
+       Okay, let's try to troubleshoot this further. Have you noticed any changes in your usage patterns or installed any new apps recently?
+       CUSTOMER
+       00:00:45
+       No, I don't think so. I've been using my phone the same way as always.
+       AGENT
+       00:00:55
+       Alright. In that case, it's possible that there might be an issue with the battery itself. I'm going to go ahead and send you a replacement battery.
+       CUSTOMER
+       00:01:05
+       Okay, that sounds good. How long will it take to arrive?
+       AGENT
+       00:01:15
+       You should receive it within 3-5 business days. In the meantime, I can also provide you with some tips on how to extend your battery life.
+       CUSTOMER
+       00:01:25
+       Yeah, that would be great. Thanks for your help.
+       AGENT
+       00:01:35
+       You're welcome. Is there anything else I can assist you with today?
+       CUSTOMER
+       00:01:45
+       No, that's all. Thanks again.
+       AGENT
+       00:01:55
+       You're welcome. Have a great day."</t>
+  </si>
+  <si>
+    <t>The customer's tone is calm and factual throughout the conversation, with a focus on describing the issue and seeking a solution. They express gratitude and appreciation for the agent's help, but do not display any strong emotions such as joy, sadness, anger, or fear.</t>
+  </si>
+  <si>
+    <t>transcript78</t>
+  </si>
+  <si>
+    <t>The customer is calling about a specific issue with their phone's battery, and the agent is able to resolve the issue by sending a replacement battery. The customer's tone is neutral and they do not express any frustration or dissatisfaction with the service.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon. I'm having some issues with the audio quality on my calls. It's been really poor lately and I'm getting frustrated.
+     AGENT
+     00:00:15
+     I apologize for the inconvenience. Can you tell me more about the issues you're experiencing? What kind of problems are you having with the audio quality?
+     CUSTOMER
+     00:00:25
+     Well, there's a lot of static and crackling. Sometimes I can barely hear the person on the other end. It's really annoying.
+     AGENT
+     00:00:35
+     I understand how frustrating that must be. Have you tried restarting your device or checking your internet connection?
+     CUSTOMER
+     00:00:45
+     Yeah, I've tried all that. It doesn't seem to make a difference. I'm starting to think it's a problem with your service.
+     AGENT
+     00:00:55
+     I apologize if our service is not meeting your expectations. I'm going to check on some things on our end. Can you please confirm your account information so I can look into this further?
+     CUSTOMER
+     00:01:05
+     Okay... it's 123456.
+     AGENT
+     00:01:15
+     Thank you. I've checked on our system and it looks like there was an outage in your area last week that may have affected your call quality. We're working to resolve the issue as soon as possible.
+     CUSTOMER
+     00:01:25
+     An outage? That's not what I want to hear. I need reliable service for my business. This is unacceptable.
+     AGENT
+     00:01:35
+     I understand your concerns and I apologize again for the inconvenience. I'm going to escalate this issue to our advanced technical support team. They'll work with you to resolve the issue as soon as possible.
+     CUSTOMER
+     00:01:45
+     Okay... I hope so. I'm not sure how much longer I can deal with this.
+     AGENT
+     00:01:55
+     I completely understand. I'm going to provide you with a reference number for your case. Please hold for just a moment while I transfer you to our advanced technical support team.
+     CUSTOMER
+     00:02:05
+     Fine.
+     AGENT
+     00:02:10
+     Thank you for holding. I've transferred you to our advanced technical support team. They'll work with you to resolve the issue with your audio quality.
+     CUSTOMER
+     00:02:15
+     Okay... thank you, I guess."</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration, annoyance, and disappointment throughout the conversation, using words like 'frustrated', 'annoying', and 'unacceptable'. Their tone is critical and complaining, indicating a strong emotional response.</t>
+  </si>
+  <si>
+    <t>transcript79</t>
+  </si>
+  <si>
+    <t>The customer is experiencing poor audio quality on their calls, with static and crackling, and has tried troubleshooting steps without success. The agent apologizes for the inconvenience and checks on the issue, discovering an outage in the customer's area that may have caused the problem. The agent escalates the issue to advanced technical support and provides a reference number for the customer's case.</t>
+  </si>
+  <si>
+    <t>I'm not sure how much longer I can deal with this.</t>
+  </si>
+  <si>
+    <t>Customer is frustrated with the service and expresses uncertainty about continuing with the company, but does not explicitly mention switching.</t>
+  </si>
+  <si>
+    <t>"AGENT
+00:00:00
+Hello good afternoon.
+CUSTOMER
+00:00:07
+good afternoon. I'm having some issues with my internet connection. It's been dropping out frequently and I'm not sure why.
+AGENT
+00:00:15
+Sorry to hear that. Can you tell me a little bit more about what's been happening? How often has it been dropping out?
+CUSTOMER
+00:00:23
+Well, it's been happening a lot. Like, every few hours. And it's not just my laptop, it's all my devices. My phone, my TV, everything.
+AGENT
+00:00:33
+Okay. Have you tried restarting your router or modem at all?
+CUSTOMER
+00:00:40
+Yeah, I've tried that. It doesn't seem to make a difference. The connection just drops out again after a little while.
+AGENT
+00:00:48
+I see. In that case, I'm going to go ahead and run some tests on our end to see if there are any issues with the connection. Can you please confirm your account information so I can look into it further?
+CUSTOMER
+00:01:00
+Yeah, it's under my name, John Smith.
+AGENT
+00:01:05
+Okay, John. I've run the tests and it looks like there may be an issue with the fiber connection in your area. I'm going to go ahead and dispatch a technician to come take a look at it.
+CUSTOMER
+00:01:15
+Okay, that sounds good. How long will it take for them to come out?
+AGENT
+00:01:20
+We should be able to get someone out to you within the next 24-48 hours. Would you like me to schedule a specific time for the appointment?
+CUSTOMER
+00:01:27
+Yeah, that would be great. How about tomorrow afternoon?
+AGENT
+00:01:32
+I've scheduled the appointment for tomorrow afternoon. You should receive a confirmation email with the details shortly. Is there anything else I can assist you with today, John?
+CUSTOMER
+00:01:40
+No, that's all. Thanks for your help.
+AGENT
+00:01:43
+You're welcome, John. We'll get that connection issue resolved for you as soon as possible. Have a great day."</t>
+  </si>
+  <si>
+    <t>The customer's tone is calm and factual throughout the conversation, with a focus on describing the issue and seeking a resolution. They do not express strong emotions such as anger, sadness, or joy, and their language is straightforward and informative.</t>
+  </si>
+  <si>
+    <t>transcript80</t>
+  </si>
+  <si>
+    <t>Customer, John Smith, is experiencing frequent internet connection drops across all devices. After troubleshooting, it was determined that there may be an issue with the fiber connection in his area. A technician has been dispatched to resolve the issue, and an appointment has been scheduled for the next day.</t>
+  </si>
+  <si>
+    <t>The customer is calling about an issue with their internet connection, but the agent is able to resolve the issue and schedule a technician visit. The customer's tone is not angry or frustrated, and there is no mention of switching companies.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon. I'm calling because I've been experiencing some issues with my internet connection. It's been slow and intermittent, and I'm getting frustrated.
+     AGENT
+     00:00:15
+     Sorry to hear that. Can you tell me more about the issue you're experiencing? When did it start, and have you noticed any patterns?
+     CUSTOMER
+     00:00:25
+     It started about a week ago. Sometimes it's fast, but most of the time it's slow. I've tried restarting my router, but that doesn't seem to make a difference.
+     AGENT
+     00:00:35
+     Okay, I'm going to check on the status of our network in your area. Can you please confirm your account information and the type of internet plan you have?
+     CUSTOMER
+     00:00:45
+     Yeah, my account number is 123456, and I have the premium plan.
+     AGENT
+     00:00:55
+     Thank you. I've checked on our network, and it looks like there's an outage in your area. Our team is working on it, but I can offer you a credit on your next bill for the inconvenience.
+     CUSTOMER
+     00:01:05
+     That's not good enough. I need a reliable internet connection for my work. Can you do anything else to fix the issue faster?
+     AGENT
+     00:01:15
+     I understand your concern. Let me escalate this issue to our advanced technical support team. They'll work on a priority basis to resolve the issue as soon as possible.
+     CUSTOMER
+     00:01:25
+     Okay, that sounds better. How long will it take to resolve?
+     AGENT
+     00:01:35
+     Our technical support team will work on it, and you should see an improvement within the next 24 to 48 hours.
+     CUSTOMER
+     00:01:45
+     Alright, I appreciate your help. But if I don't see an improvement, I'll have to consider switching to a different provider.
+     AGENT
+     00:01:55
+     I completely understand, and I apologize again for the inconvenience. If you have any further issues, please don't hesitate to reach out to us. We value your business and want to ensure you're satisfied with our service.
+     CUSTOMER
+     00:02:05
+     Okay, thank you.
+     AGENT
+     00:02:10
+     You're welcome. Have a great day."</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration and annoyance throughout the conversation, particularly when discussing the slow and intermittent internet connection, and when considering switching to a different provider. The customer's tone is assertive and demanding, indicating a strong emotional response.</t>
+  </si>
+  <si>
+    <t>transcript81</t>
+  </si>
+  <si>
+    <t>Customer reported slow and intermittent internet connection. Agent checked network status, confirmed outage, and offered credit on next bill. Customer escalated issue to advanced technical support team, and agent provided estimated resolution time of 24-48 hours.</t>
+  </si>
+  <si>
+    <t>I'll have to consider switching to a different provider</t>
+  </si>
+  <si>
+    <t>The customer is frustrated with the internet connection issues and is considering switching to a different provider if the issue is not resolved, indicating a medium level of churn.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon. I'm having some issues with my laptop's battery. It's not holding a charge like it used to.
+     AGENT
+     00:00:15
+     Sorry to hear that. Can you tell me more about the issue you're experiencing? How old is your laptop?
+     CUSTOMER
+     00:00:23
+     It's about 2 years old. And the battery life has been decreasing over the past few months. Now it can barely last an hour.
+     AGENT
+     00:00:32
+     I see. Have you tried calibrating the battery or updating your laptop's BIOS?
+     CUSTOMER
+     00:00:40
+     No, I haven't tried that. I'm not very tech-savvy. Can you walk me through the process?
+     AGENT
+     00:00:48
+     Of course! Calibrating the battery is a simple process. I can guide you through it. But before that, can you tell me what kind of laptop you have?
+     CUSTOMER
+     00:00:56
+     It's a Dell Inspiron.
+     AGENT
+     00:01:02
+     Okay. For a Dell Inspiron, you'll need to let the battery drain to 0% and then charge it to 100%. You'll need to repeat this process a few times to calibrate the battery.
+     CUSTOMER
+     00:01:12
+     Okay, that sounds doable. But what if that doesn't work? I'm worried that I might need to replace the battery.
+     AGENT
+     00:01:20
+     If calibrating the battery doesn't work, it's possible that the battery is faulty and needs to be replaced. But let's try the calibration process first and see if that resolves the issue.
+     CUSTOMER
+     00:01:29
+     Okay. And how long does the calibration process take?
+     AGENT
+     00:01:36
+     It should only take a few hours. But if you're still experiencing issues after that, we can discuss further options, including replacing the battery.
+     CUSTOMER
+     00:01:44
+     Okay, I'll try that. Thanks for your help.
+     AGENT
+     00:01:50
+     You're welcome! If you have any more questions or need further assistance, don't hesitate to reach out. Have a great day!
+     CUSTOMER
+     00:01:57
+     Thanks, you too.
+     "</t>
+  </si>
+  <si>
+    <t>The customer's tone is calm and factual throughout the conversation, with a neutral emotional tone. They express concern and worry about the issue with their laptop's battery, but the agent's guidance and explanations help to alleviate their concerns. The customer's language is polite and appreciative, but there is no strong emotional expression.</t>
+  </si>
+  <si>
+    <t>transcript82</t>
+  </si>
+  <si>
+    <t>Customer's laptop battery is not holding a charge, and the agent suggests calibrating the battery by letting it drain to 0% and then charging it to 100%. If that doesn't work, the agent suggests replacing the battery.</t>
+  </si>
+  <si>
+    <t>The customer is calling about a specific issue with their laptop's battery, and the agent is providing helpful solutions. The customer's tone is neutral and they do not express any frustration or dissatisfaction with the company.</t>
+  </si>
+  <si>
+    <t>"AGENT
+00:00:00
+Hello good afternoon.
+CUSTOMER
+00:00:07
+good afternoon. I'm having some issues with the software. It's been freezing on me a lot lately.
+AGENT
+00:00:14
+Sorry to hear that. Can you tell me more about the issue you're experiencing? What kind of error messages are you seeing?
+CUSTOMER
+00:00:21
+Well, it just freezes. There's no error message or anything. I'll be in the middle of working on something and suddenly the whole program just locks up.
+AGENT
+00:00:30
+I see. Have you tried restarting the program or your computer to see if that resolves the issue?
+CUSTOMER
+00:00:37
+Yeah, I've tried that. It doesn't seem to make a difference. It still freezes up after a while.
+AGENT
+00:00:44
+Okay. Let me see what I can do to help you. Can you tell me what version of the software you're running?
+CUSTOMER
+00:00:51
+Uh, let me check. *pause* Okay, it says I'm running version 2.5.
+AGENT
+00:01:00
+Alright. We did have some issues with freezing in that version. I'm going to go ahead and send you a patch to update to the latest version. That should resolve the issue.
+CUSTOMER
+00:01:09
+Okay, that sounds good. How do I go about installing the patch?
+AGENT
+00:01:15
+I'll send you a link to download the patch. Once you've downloaded it, just follow the prompts to install it. It should only take a few minutes.
+CUSTOMER
+00:01:23
+Alright, got it. Thanks for your help.
+AGENT
+00:01:29
+You're welcome. If you have any more issues or need further assistance, don't hesitate to reach out. Have a great day.
+CUSTOMER
+00:01:36
+You too. Bye.
+AGENT
+00:01:40
+Bye."</t>
+  </si>
+  <si>
+    <t>The customer's tone is calm and factual throughout the conversation, describing the issue with the software and seeking a solution. They don't express any strong emotions, such as frustration or disappointment, but rather a neutral and matter-of-fact approach to resolving the problem.</t>
+  </si>
+  <si>
+    <t>transcript83</t>
+  </si>
+  <si>
+    <t>The customer was experiencing frequent freezing issues with the software, which was resolved by updating to the latest version via a patch sent by the agent. The customer was provided with instructions on how to download and install the patch.</t>
+  </si>
+  <si>
+    <t>The customer is calling about a specific issue with the software, and the agent is able to resolve the issue by providing a patch to update to the latest version. The customer's tone is not angry or frustrated, and there is no mention of switching companies.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon
+     AGENT
+     00:00:10
+     How can I assist you today?
+     CUSTOMER
+     00:00:15
+     I had an incident with my car and I want to report it for physical damage.
+     AGENT
+     00:00:20
+     Sorry to hear that. Can you please provide me with your policy number so I can assist you further?
+     CUSTOMER
+     00:00:25
+     It's 1234567890.
+     AGENT
+     00:00:30
+     Thank you. Can you please describe what happened to your car?
+     CUSTOMER
+     00:00:35
+     I was parked on the street and someone hit my car and drove away. I didn't see who it was.
+     AGENT
+     00:00:40
+     I see. Did you file a police report?
+     CUSTOMER
+     00:00:45
+     Yes, I did. The officer gave me a copy of the report.
+     AGENT
+     00:00:50
+     Okay. We'll need that report to process your claim. Can you please fax or email it to us?
+     CUSTOMER
+     00:00:55
+     Yeah, I can do that. What's the fax number or email address?
+     AGENT
+     00:01:00
+     The fax number is 555-555-5555 and the email address is claims@insurancecompany.com.
+     CUSTOMER
+     00:01:05
+     Got it. I'll send it over right away.
+     AGENT
+     00:01:10
+     Great, thank you. We'll review the report and get back to you within 24-48 hours to let you know the next steps.
+     CUSTOMER
+     00:01:15
+     Okay, sounds good. Thanks for your help.
+     AGENT
+     00:01:20
+     You're welcome. Is there anything else I can assist you with today?
+     CUSTOMER
+     00:01:25
+     No, that's all. Thanks again.
+     AGENT
+     00:01:30
+     You're welcome. Have a great day."</t>
+  </si>
+  <si>
+    <t>The customer's tone is calm and factual throughout the conversation, providing necessary information and following the agent's instructions without expressing any strong emotions.</t>
+  </si>
+  <si>
+    <t>transcript84</t>
+  </si>
+  <si>
+    <t>The customer reported a physical damage incident with their car, which was hit by another vehicle while parked on the street. The customer filed a police report and will send the report to the insurance company via fax or email. The insurance company will review the report and contact the customer within 24-48 hours to discuss the next steps.</t>
+  </si>
+  <si>
+    <t>The customer is calling to report an incident with their car and the agent is assisting them with the process. The tone of the conversation is neutral and there is no indication of churn.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon
+     AGENT
+     00:00:10
+     Thank you for reaching out to us. My name is Alex, and I'll be happy to assist you with any issues you're experiencing. What seems to be the problem today?
+     CUSTOMER
+     00:00:20
+     Hi Alex, thanks for taking my call. I'm having some issues with my internet connection. It's been dropping out frequently throughout the day.
+     AGENT
+     00:00:30
+     Sorry to hear that. Can you tell me a little bit more about what's been happening? For example, how often does it drop out, and have you noticed any patterns or error messages?
+     CUSTOMER
+     00:00:40
+     Yeah, it's been happening pretty regularly, maybe every 30 minutes or so. And I haven't seen any error messages, it just seems to stop working.
+     AGENT
+     00:00:50
+     Okay, I see. Have you tried restarting your router or modem to see if that resolves the issue?
+     CUSTOMER
+     00:01:00
+     Yeah, I've tried that a few times, but it doesn't seem to make a difference.
+     AGENT
+     00:01:10
+     Alright. In that case, I'd like to run some tests on your connection to see if we can identify the problem. Can you please confirm your account information so I can access your account?
+     CUSTOMER
+     00:01:20
+     Sure thing. My account number is 123456.
+     AGENT
+     00:01:30
+     Thank you. I've accessed your account, and I'm running some tests now. (pause) Okay, it looks like there may be an issue with the connection in your area. I'm going to go ahead and send a signal to your router to try and resolve the issue.
+     CUSTOMER
+     00:02:00
+     Okay, sounds good. How long will that take?
+     AGENT
+     00:02:10
+     It should only take a few minutes. In the meantime, I'd like to offer you a one-time courtesy credit on your account for the inconvenience you've experienced.
+     CUSTOMER
+     00:02:20
+     That's great, thank you.
+     AGENT
+     00:02:30
+     You're welcome. I'll go ahead and apply the credit now. (pause) Okay, the signal has been sent, and your connection should be restored shortly. Is there anything else I can assist you with today?
+     CUSTOMER
+     00:02:40
+     No, that's all. Thanks again for your help, Alex.
+     AGENT
+     00:02:50
+     You're welcome. It was my pleasure to assist you. If you experience any further issues, don't hesitate to reach out to us. Have a great day!
+     CUSTOMER
+     00:03:00
+     You too, thanks."</t>
+  </si>
+  <si>
+    <t>The customer's tone is calm and factual throughout the conversation, with a focus on describing the issue and seeking resolution. They express gratitude and appreciation for the agent's help, but do not display strong emotions such as joy, sadness, anger, fear, disgust, or surprise.</t>
+  </si>
+  <si>
+    <t>transcript85</t>
+  </si>
+  <si>
+    <t>Customer reported frequent internet connection drops. Agent ran tests, identified issue with connection in the area, and sent a signal to resolve the issue. Provided a one-time courtesy credit for the inconvenience experienced.</t>
+  </si>
+  <si>
+    <t>The customer is calling about an issue with their internet connection, but the agent is able to resolve the issue and offer a courtesy credit, and the customer is satisfied with the resolution.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon. I'm having some issues with my internet connection. It's been slow and intermittent all day.
+     AGENT
+     00:00:15
+     Sorry to hear that. Can you tell me a little bit more about what's been going on? When did you first notice the issue?
+     CUSTOMER
+     00:00:25
+     It started this morning. I was trying to work from home and I couldn't even load a webpage. It's been on and off all day.
+     AGENT
+     00:00:35
+     Okay, I see. Have you tried restarting your router or modem at all?
+     CUSTOMER
+     00:00:42
+     Yeah, I've tried that a few times. It seems to work for a little bit, but then it slows down again.
+     AGENT
+     00:00:50
+     Alright. I'm going to go ahead and run a few tests on our end to see if there's any issues with the connection. Can you please confirm your account information for me?
+     CUSTOMER
+     00:01:00
+     Yeah, it's under John Doe.
+     AGENT
+     00:01:05
+     Okay, thank you. I'm showing that there is an issue with the connection in your area. I'm going to go ahead and dispatch a technician to come take a look at it.
+     CUSTOMER
+     00:01:15
+     Okay, that sounds good. How long until they can come out?
+     AGENT
+     00:01:20
+     We can have someone out to you within the next 24-48 hours. Would you prefer a morning or afternoon appointment?
+     CUSTOMER
+     00:01:25
+     Afternoon is fine.
+     AGENT
+     00:01:30
+     Alright, I've scheduled the appointment for tomorrow afternoon. You should receive a call from the technician an hour before they arrive to confirm. Is there anything else I can assist you with today?
+     CUSTOMER
+     00:01:40
+     No, that's it. Thanks for your help.
+     AGENT
+     00:01:45
+     You're welcome. I apologize again for the inconvenience and appreciate your patience. Have a good day.
+     CUSTOMER
+     00:01:50
+     You too.
+     "</t>
+  </si>
+  <si>
+    <t>The customer's tone is calm and factual throughout the conversation, with a focus on describing the issue and seeking resolution. They do not express strong emotions such as frustration, disappointment, or happiness, but rather a neutral and matter-of-fact tone.</t>
+  </si>
+  <si>
+    <t>transcript86</t>
+  </si>
+  <si>
+    <t>Customer reported slow and intermittent internet connection. Technician dispatched to investigate and scheduled appointment for the next day. Customer's account information confirmed and appointment details provided.</t>
+  </si>
+  <si>
+    <t>It's been slow and intermittent all day.</t>
+  </si>
+  <si>
+    <t>The customer is frustrated with the internet connection, but the issue is being resolved and the agent is apologetic, showing a minor dissatisfaction.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon
+     AGENT
+     00:00:10
+     Thank you for reaching out to us. How can I assist you today?
+     CUSTOMER
+     00:00:15
+     Yeah, I'm having some issues with my internet connection. It's been really slow lately.
+     AGENT
+     00:00:20
+     Sorry to hear that. Can you tell me more about the issue you're experiencing? When did it start and have you noticed any patterns?
+     CUSTOMER
+     00:00:30
+     It started about a week ago. Sometimes it's fast, but most of the time it's really slow. I've tried restarting my router, but it doesn't seem to make a difference.
+     AGENT
+     00:00:40
+     Okay, I'm going to go ahead and check on the status of our network in your area. Can you please confirm your account information so I can look into this further?
+     CUSTOMER
+     00:00:50
+     Yeah, my account number is 123456.
+     AGENT
+     00:01:00
+     Thank you. I've checked on the status of our network, and it looks like there's an outage in your area. Our team is working to resolve the issue as soon as possible.
+     CUSTOMER
+     00:01:10
+     Okay, that's good to know. Do you know when it's expected to be fixed?
+     AGENT
+     00:01:15
+     Our team is working diligently to resolve the issue, and we expect it to be fixed within the next 24-48 hours.
+     CUSTOMER
+     00:01:20
+     Okay, that's a bit longer than I was hoping for. Is there anything you can do to help me in the meantime?
+     AGENT
+     00:01:25
+     I can offer you a one-time credit on your account for the inconvenience. Would you like me to apply that for you?
+     CUSTOMER
+     00:01:30
+     Yeah, that would be great. Thank you.
+     AGENT
+     00:01:35
+     You're welcome. I've applied the credit to your account. Is there anything else I can assist you with today?
+     CUSTOMER
+     00:01:40
+     No, that's all. Thank you for your help.
+     AGENT
+     00:01:45
+     You're welcome. It was my pleasure to assist you. If you have any other issues or concerns, please don't hesitate to reach out to us.
+     "</t>
+  </si>
+  <si>
+    <t>The customer's tone is calm and factual throughout the conversation, with a focus on resolving the issue and seeking assistance. Although they express some frustration with the expected resolution time, their language remains neutral and polite.</t>
+  </si>
+  <si>
+    <t>transcript87</t>
+  </si>
+  <si>
+    <t>a bit longer than I was hoping for</t>
+  </si>
+  <si>
+    <t>The customer is showing minor dissatisfaction with the resolution time, but the issue is being addressed and a credit is offered, which reduces the churn risk.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon, I'm having some issues with my laptop. The keyboard is not working properly.
+     AGENT
+     00:00:14
+     Sorry to hear that. Can you please tell me more about the issue you're experiencing with your keyboard?
+     CUSTOMER
+     00:00:21
+     Yeah, some of the keys are not registering when I press them. It's really frustrating.
+     AGENT
+     00:00:28
+     I understand how frustrating that can be. Have you tried restarting your laptop or updating your keyboard drivers?
+     CUSTOMER
+     00:00:35
+     Yeah, I've tried restarting, but that didn't work. And I'm not sure how to update the drivers.
+     AGENT
+     00:00:42
+     Okay, no problem. I can walk you through the process of updating your keyboard drivers. But before we do that, can you please tell me what kind of laptop you have and what operating system it's running on?
+     CUSTOMER
+     00:00:50
+     It's a Dell Inspiron and it's running on Windows 10.
+     AGENT
+     00:00:57
+     Alright. I'm going to send you a link to download the latest keyboard drivers for your laptop. Can you please click on the link and follow the instructions to install the drivers?
+     CUSTOMER
+     00:01:04
+     Okay, I've downloaded the drivers. But I'm still having the same issue.
+     AGENT
+     00:01:11
+     Okay, in that case, it's possible that there's a hardware issue with your keyboard. I'm going to go ahead and set up a repair order for you. We'll get your laptop fixed and returned to you as soon as possible.
+     CUSTOMER
+     00:01:19
+     Okay, that sounds good. But how long is that going to take?
+     AGENT
+     00:01:26
+     Typically, the repair process takes around 5-7 business days. But I'll make sure to expedite the process for you.
+     CUSTOMER
+     00:01:33
+     Alright, thank you for your help. I appreciate it.
+     AGENT
+     00:01:40
+     You're welcome. I apologize again for the inconvenience and appreciate your patience. Is there anything else I can assist you with today?
+     CUSTOMER
+     00:01:47
+     No, that's all. Thank you.
+     AGENT
+     00:01:54
+     You're welcome. Have a great day.
+     CUSTOMER
+     00:01:59
+     You too.
+     "</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration and annoyance throughout the conversation, particularly when describing the issue with their keyboard ('It's really frustrating') and when the issue persists after trying to update the drivers ('But I'm still having the same issue').</t>
+  </si>
+  <si>
+    <t>transcript88</t>
+  </si>
+  <si>
+    <t>Customer's laptop keyboard is not working properly. Agent assists customer in troubleshooting and updating keyboard drivers. Due to hardware issue, a repair order is set up, and the laptop will be fixed and returned within 5-7 business days.</t>
+  </si>
+  <si>
+    <t>The customer is frustrated with the issue, but the agent is able to resolve the issue and the customer's tone changes to appreciation.</t>
+  </si>
+  <si>
+    <t>"AGENT
+      00:00:00
+      Hello good afternoon.
+      CUSTOMER
+      00:00:07
+      good afternoon. I'm having some issues with my laptop. The keyboard is not working properly.
+      AGENT
+      00:00:15
+      Sorry to hear that. Can you please tell me more about the issue you're experiencing with your keyboard?
+      CUSTOMER
+      00:00:23
+      Yeah, sometimes the keys don't register when I press them, and sometimes they register multiple times. It's really frustrating.
+      AGENT
+      00:00:32
+      I understand how frustrating that can be. Have you tried restarting your laptop or updating your keyboard drivers?
+      CUSTOMER
+      00:00:40
+      Yeah, I've tried restarting, but I'm not sure about the drivers. I'm not very tech-savvy.
+      AGENT
+      00:00:47
+      No worries, I can walk you through it. Can you please tell me what kind of laptop you have and what operating system it's running on?
+      CUSTOMER
+      00:00:55
+      It's a Dell Inspiron, and I think it's running Windows 10.
+      AGENT
+      00:01:02
+      Okay, great. I'm going to guide you through updating your keyboard drivers. Can you please go to your start menu and search for 'device manager'?
+      CUSTOMER
+      00:01:11
+      Okay, got it.
+      AGENT
+      00:01:14
+      Now, can you please expand the 'keyboards' section and look for any devices with a yellow exclamation mark next to them?
+      CUSTOMER
+      00:01:23
+      Yeah, I see one.
+      AGENT
+      00:01:26
+      Okay, that's likely the cause of the issue. Can you please right-click on that device and select 'update driver'?
+      CUSTOMER
+      00:01:35
+      Okay, I've done that. But it's still not working properly.
+      AGENT
+      00:01:42
+      I apologize for the inconvenience. In that case, it's possible that there's a hardware issue with your keyboard. I'm going to go ahead and set up a repair order for you.
+      CUSTOMER
+      00:01:51
+      Okay, thank you. How long will that take?
+      AGENT
+      00:01:56
+      The repair process usually takes around 5-7 business days. We'll also provide you with a prepaid return shipping label so you can send the laptop back to us.
+      CUSTOMER
+      00:02:04
+      Okay, that sounds good. Thank you for your help.
+      AGENT
+      00:02:08
+      You're welcome. Is there anything else I can assist you with today?
+      CUSTOMER
+      00:02:12
+      No, that's all. Thank you again.
+      AGENT
+      00:02:15
+      You're welcome. Have a great day."</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration and annoyance with the issue they're experiencing with their laptop keyboard, using words like'really frustrating' and 'it's still not working properly'.</t>
+  </si>
+  <si>
+    <t>transcript89</t>
+  </si>
+  <si>
+    <t>Customer's laptop keyboard is not working properly. Agent guides customer through updating keyboard drivers, but issue persists. Agent sets up repair order for hardware issue.</t>
+  </si>
+  <si>
+    <t>The customer is frustrated with the issue, but the agent is able to resolve it and the customer's tone changes to appreciation.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon
+     AGENT
+     00:00:10
+     I'm so sorry to hear that you're experiencing no audio output. Can you please tell me more about the issue you're facing?
+     CUSTOMER
+     00:00:17
+     yeah, I was watching a video and suddenly the audio just stopped working. I've tried restarting my computer but it didn't work.
+     AGENT
+     00:00:25
+     I apologize for the inconvenience. Have you tried checking your audio settings or updating your audio drivers?
+     CUSTOMER
+     00:00:32
+     yeah, I've checked the settings and they seem fine. I'm not sure about updating the drivers though.
+     AGENT
+     00:00:39
+     Okay, let me guide you through the process. Can you please tell me what kind of computer you're using and what operating system it's running on?
+     CUSTOMER
+     00:00:46
+     it's a windows 10 laptop
+     AGENT
+     00:00:52
+     Alright, I'll walk you through the steps to update your audio drivers. Can you please go to your device manager and click on 'sound, video and game controllers'?
+     CUSTOMER
+     00:01:01
+     okay, I'm there
+     AGENT
+     00:01:05
+     Great! Now, can you please right-click on 'realtek audio' and select 'update driver'?
+     CUSTOMER
+     00:01:12
+     okay, it's updating now
+     AGENT
+     00:01:18
+     Okay, once the update is complete, please restart your laptop and check if the audio is working again.
+     CUSTOMER
+     00:01:25
+     okay, I'll do that. Thanks for your help!
+     AGENT
+     00:01:30
+     You're welcome! If you have any more issues or concerns, please don't hesitate to reach out to us. Have a great day!
+     CUSTOMER
+     00:01:36
+     thanks, you too"</t>
+  </si>
+  <si>
+    <t>The customer's tone is calm and cooperative throughout the conversation, even when expressing frustration about the issue. They follow the agent's instructions and show appreciation for the help, indicating a neutral emotional state.</t>
+  </si>
+  <si>
+    <t>transcript90</t>
+  </si>
+  <si>
+    <t>Customer was experiencing no audio output on their Windows 10 laptop. Agent guided the customer through updating their audio drivers, which resolved the issue.</t>
+  </si>
+  <si>
+    <t>The customer is calling about a technical issue, and the agent is able to resolve it. The customer's tone is neutral, and there is no indication of frustration or dissatisfaction that would suggest churn.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon
+     AGENT
+     00:00:10
+     Thank you for reaching out to us. How can I assist you today?
+     CUSTOMER
+     00:00:15
+     I'm having some issues with my computer. The audio isn't working.
+     AGENT
+     00:00:20
+     Sorry to hear that. Can you tell me more about the issue you're experiencing? When did it start happening?
+     CUSTOMER
+     00:00:27
+     It started yesterday. I was watching a video and suddenly the audio just stopped working.
+     AGENT
+     00:00:33
+     Have you tried restarting your computer or checking the audio settings?
+     CUSTOMER
+     00:00:39
+     Yeah, I've tried restarting and checking the settings, but nothing seems to work.
+     AGENT
+     00:00:44
+     Okay. Let me see what I can do to help you. Can you please tell me what kind of computer you're using and what operating system it's running on?
+     CUSTOMER
+     00:00:51
+     It's a Dell laptop running on Windows 10.
+     AGENT
+     00:00:56
+     Alright. I'm going to walk you through some troubleshooting steps. First, let's try updating your audio drivers. Have you done that recently?
+     CUSTOMER
+     00:01:03
+     No, I haven't updated them in a while.
+     AGENT
+     00:01:07
+     Okay. I'll guide you through the process. Please follow my instructions carefully.
+     CUSTOMER
+     00:01:12
+     Okay...
+     AGENT
+     00:01:15
+     Great. I think we're making progress. If the issue persists after updating the drivers, we may need to look into other solutions. But let's try this first and see how it goes.
+     CUSTOMER
+     00:01:22
+     Alright. Thanks for your help so far.
+     AGENT
+     00:01:25
+     You're welcome. I'm happy to assist you. If you have any other questions or need further assistance, please don't hesitate to ask."</t>
+  </si>
+  <si>
+    <t>The customer's tone is calm and factual throughout the conversation, without expressing any strong emotions such as happiness, frustration, or disappointment. They provide necessary information and follow the agent's instructions, indicating a neutral emotional state.</t>
+  </si>
+  <si>
+    <t>transcript91</t>
+  </si>
+  <si>
+    <t>Customer is experiencing audio issues on their Dell laptop running Windows 10. Agent assists customer in troubleshooting steps, including updating audio drivers, to resolve the issue.</t>
+  </si>
+  <si>
+    <t>The customer is calling about a technical issue with their computer, and the agent is providing troubleshooting steps to resolve the issue. The customer tone is neutral and there is no indication of frustration or anger towards the company.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon. I'm having some issues with the audio quality on my recent calls. It's been really poor and I'm not sure what's going on.
+     AGENT
+     00:00:15
+     Sorry to hear that. Can you tell me more about the issue you're experiencing? Is it static, echoing, or something else?
+     CUSTOMER
+     00:00:22
+     It's just really fuzzy and hard to hear. I've tried using different headphones and even switching to a different device, but nothing seems to work.
+     AGENT
+     00:00:30
+     I see. Have you tried checking your internet connection speed? Sometimes a slow connection can cause poor audio quality.
+     CUSTOMER
+     00:00:37
+     Yeah, I've checked that. My internet speed is fine. I'm not sure what's going on.
+     AGENT
+     00:00:43
+     Okay. Let me check on our end to see if there are any issues with our servers. Can you please confirm your account information so I can look into this further?
+     CUSTOMER
+     00:00:51
+     Yeah, my account number is 123456.
+     AGENT
+     00:00:56
+     Thank you. I've checked on our end and it looks like there was an issue with our servers earlier today. We've since resolved the issue, but I'd like to offer you a complimentary call quality test to ensure everything is working properly now.
+     CUSTOMER
+     00:01:04
+     Okay, that sounds good. How do I do that?
+     AGENT
+     00:01:08
+     I can walk you through it. It'll just take a few minutes. Are you ready to do that now?
+     CUSTOMER
+     00:01:12
+     Yeah, I'm ready.
+     AGENT
+     00:01:15
+     Great. I'll guide you through the process. First, can you please click on the 'settings' icon on your dashboard and select 'audio settings'?
+     CUSTOMER
+     00:01:22
+     Okay, got it.
+     AGENT
+     00:01:25
+     Now, can you please click on the 'test audio' button?
+     CUSTOMER
+     00:01:30
+     Okay, I've clicked it. What now?
+     AGENT
+     00:01:33
+     You should hear a test tone playing. Is the audio clear and crisp?
+     CUSTOMER
+     00:01:38
+     Yeah, it sounds much better now. Thanks for your help!
+     AGENT
+     00:01:42
+     You're welcome! I'm glad we could resolve the issue. If you have any other problems, don't hesitate to reach out. Have a great day!
+     CUSTOMER
+     00:01:46
+     Thanks, you too."</t>
+  </si>
+  <si>
+    <t>The customer's tone is calm and factual throughout the conversation, with a focus on describing the issue and seeking a resolution. They express frustration and disappointment with the poor audio quality, but their language remains neutral and objective.</t>
+  </si>
+  <si>
+    <t>transcript92</t>
+  </si>
+  <si>
+    <t>Customer reported poor audio quality on recent calls. Agent investigated and found an issue with the company's servers, which was resolved. A complimentary call quality test was offered to ensure everything was working properly. The customer's audio quality was tested and found to be clear and crisp after the test.</t>
+  </si>
+  <si>
+    <t>The customer's issue was resolved, and they expressed gratitude towards the agent. The tone of the conversation remained polite and courteous throughout.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon
+     AGENT
+     00:00:10
+     How can I assist you today?
+     CUSTOMER
+     00:00:15
+     I'm having some issues with my laptop's keyboard. Some keys are not working properly.
+     AGENT
+     00:00:22
+     Sorry to hear that. Can you please tell me more about the issue? Which keys are not working?
+     CUSTOMER
+     00:00:30
+     The 'e' and 't' keys are not registering when I press them.
+     AGENT
+     00:00:37
+     Have you tried cleaning the keyboard or checking for any debris that might be causing the issue?
+     CUSTOMER
+     00:00:44
+     Yes, I've tried cleaning it, but the problem persists.
+     AGENT
+     00:00:50
+     Okay. In that case, it's possible that there's a hardware issue with the keyboard. I'm going to go ahead and troubleshoot some more with you. Can you please try pressing the 'e' and 't' keys simultaneously and see if they register then?
+     CUSTOMER
+     00:01:02
+     Okay... yeah, they're still not working.
+     AGENT
+     00:01:07
+     Alright. I'm going to go ahead and escalate this issue to our advanced technical support team. They'll be able to assist you further with the hardware issue. Would you like me to set up a callback or would you prefer to continue chatting with me?
+     CUSTOMER
+     00:01:17
+     A callback would be great, thank you.
+     AGENT
+     00:01:22
+     You're welcome. I've set up a callback for you. Someone from our advanced technical support team will be in touch with you within the next 24-48 hours to assist you further. Is there anything else I can assist you with in the meantime?
+     CUSTOMER
+     00:01:30
+     No, that's all. Thank you for your help.
+     AGENT
+     00:01:34
+     You're welcome. Have a great day!"</t>
+  </si>
+  <si>
+    <t>The customer's language and tone throughout the conversation are calm and factual, without expressing any strong emotions such as happiness, frustration, or disappointment. They report the issue with their laptop's keyboard and follow the agent's instructions to troubleshoot the problem. The customer's responses are polite and appreciative, but they do not show any strong emotional tone.</t>
+  </si>
+  <si>
+    <t>transcript93</t>
+  </si>
+  <si>
+    <t>Customer had issues with laptop keyboard, specifically 'e' and 't' keys not working. Agent tried troubleshooting, but issue persisted, so it was escalated to advanced technical support team for further assistance.</t>
+  </si>
+  <si>
+    <t>The customer is calling about a technical issue with their laptop's keyboard, and the agent is assisting them with troubleshooting and escalating the issue to advanced technical support. The customer's tone is neutral and they do not express any frustration or dissatisfaction with the service.</t>
+  </si>
+  <si>
+    <t>"AGENT
+00:00:00
+Hello good afternoon.
+CUSTOMER
+00:00:07
+good afternoon. I'm having some issues with the audio quality on my calls. It's been really poor lately.
+AGENT
+00:00:14
+Sorry to hear that. Can you tell me more about the issue you're experiencing? Is it on all calls or just certain ones?
+CUSTOMER
+00:00:22
+It's on all calls. I've tried using different headsets and even different devices, but the problem persists.
+AGENT
+00:00:31
+I see. Have you tried checking your internet connection speed? Sometimes a slow connection can cause audio quality issues.
+CUSTOMER
+00:00:40
+Yeah, I've checked that. My internet speed is fine. I'm not sure what's causing the problem.
+AGENT
+00:00:48
+Okay. Let me check on our end to see if there are any issues with our servers. Can you please confirm your account information so I can look into this further?
+CUSTOMER
+00:00:57
+Yeah, it's account number 12345.
+AGENT
+00:01:04
+Thank you. I've checked on our end, and it looks like there was an issue with our servers that may have been causing the poor audio quality. I've gone ahead and reset your account, so you should start seeing improvements soon.
+CUSTOMER
+00:01:17
+Okay, that sounds good. But what if it doesn't improve? I'm getting really frustrated with this issue.
+AGENT
+00:01:25
+I completely understand. If you're still experiencing issues after the reset, please don't hesitate to reach out to us again. We'll do everything we can to resolve the problem as quickly as possible.
+CUSTOMER
+00:01:35
+Alright. Thanks for your help.
+AGENT
+00:01:40
+You're welcome. Is there anything else I can assist you with today?
+CUSTOMER
+00:01:45
+No, that's all. Thanks again.
+AGENT
+00:01:49
+You're welcome. Have a great day."</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration and annoyance with the issue they're experiencing, using phrases like 'I'm getting really frustrated with this issue' and 'it's been really poor lately'. This indicates a strong negative emotion, which is characteristic of anger.</t>
+  </si>
+  <si>
+    <t>transcript94</t>
+  </si>
+  <si>
+    <t>The customer reported poor audio quality on all calls, which was investigated by the agent. The agent checked the customer's internet connection speed and the company's servers, and found an issue with the servers that was causing the problem. The agent reset the customer's account, and advised them to contact the company again if the issue persisted.</t>
+  </si>
+  <si>
+    <t>I'm getting really frustrated with this issue</t>
+  </si>
+  <si>
+    <t>Customer is frustrated with the audio quality issue, but the agent is able to resolve the issue and provide a solution, which reduces the churn risk to low.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon. I'm having some issues with my internet connection. It's been slow and dropping out frequently.
+     AGENT
+     00:00:15
+     Sorry to hear that. Can you please tell me more about the issue you're experiencing? When did it start and have you tried restarting your router?
+     CUSTOMER
+     00:00:25
+     Yeah, I've tried restarting the router multiple times, but it doesn't seem to make a difference. It started about a week ago. I've also tried using a different device, but the issue persists.
+     AGENT
+     00:00:37
+     Okay, I'm going to go ahead and check on the status of our network in your area. Can you please provide me with your account information so I can look into this further?
+     CUSTOMER
+     00:00:45
+     My account number is 123456. I'm really frustrated with this issue, I need a reliable internet connection for work.
+     AGENT
+     00:00:55
+     I understand your frustration, and I apologize for the inconvenience. I've checked on our network, and it appears that there's an outage in your area. Our team is working to resolve the issue as soon as possible.
+     CUSTOMER
+     00:01:05
+     An outage? How long is it going to take to fix? I've been dealing with this for a week already.
+     AGENT
+     00:01:13
+     I understand your concern. I've escalated the issue to our advanced technical support team, and they'll be in touch with you within the next 24 hours to provide a more detailed timeline for the resolution.
+     CUSTOMER
+     00:01:23
+     24 hours? That's unacceptable. I need a solution now. I'm considering switching to a different provider if this issue isn't resolved quickly.
+     AGENT
+     00:01:33
+     I understand your concern, and I apologize again for the inconvenience. I'm going to go ahead and offer you a one-time credit on your account for the trouble you've experienced. Would you like me to also schedule a technician visit to ensure the issue is resolved as soon as possible?
+     CUSTOMER
+     00:01:45
+     Yeah, schedule the visit. But I'm still not sure if I want to continue with your service. I'll need to think about it.
+     AGENT
+     00:01:55
+     I understand, and I appreciate your honesty. I'm going to go ahead and schedule the visit for tomorrow. In the meantime, I'll also make sure to follow up with you to ensure the issue is resolved to your satisfaction. Is there anything else I can assist you with today?
+     CUSTOMER
+     00:02:05
+     No, that's all. Thank you.
+     AGENT
+     00:02:10
+     You're welcome. We'll get this issue resolved for you as soon as possible. Have a good day.
+     "</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration and annoyance throughout the conversation, particularly when discussing the duration of the issue and the proposed resolution timeline. They also explicitly state their frustration and concern, using phrases like 'I'm really frustrated with this issue' and 'That's unacceptable'.</t>
+  </si>
+  <si>
+    <t>transcript95</t>
+  </si>
+  <si>
+    <t>Customer reported slow and dropping internet connection, agent checked network status and found outage in customer's area, escalated issue to advanced technical support team, offered one-time credit and scheduled technician visit to resolve issue.</t>
+  </si>
+  <si>
+    <t>I'm considering switching to a different provider if this issue isn't resolved quickly</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon. I am calling to report some physical damage to my property. 
+     AGENT
+     00:00:15
+     Sorry to hear that. Can you please provide me with more details about the damage?
+     CUSTOMER
+     00:00:23
+     Yes, of course. I had a pipe burst in my basement and it caused a lot of water damage. 
+     AGENT
+     00:00:32
+     I apologize for the inconvenience. Have you had a chance to document the damage with photos or videos?
+     CUSTOMER
+     00:00:40
+     Yes, I have taken some photos and videos. I can send them to you if you'd like.
+     AGENT
+     00:00:48
+     That would be great, thank you. Can you also tell me a little bit more about what happened? 
+     CUSTOMER
+     00:00:56
+     Well, I woke up in the morning and found that my basement was flooded. I'm not sure when it happened, but I think it was sometime during the night. 
+     AGENT
+     00:01:05
+     Okay, got it. And have you had a chance to get an estimate for the repairs?
+     CUSTOMER
+     00:01:12
+     Not yet, but I plan on getting one soon. 
+     AGENT
+     00:01:19
+     Alright. I'm going to go ahead and file a claim for you. We'll get an adjuster out to assess the damage and get the process started. 
+     CUSTOMER
+     00:01:28
+     Okay, that sounds good. Thank you for your help.
+     AGENT
+     00:01:34
+     You're welcome. Is there anything else I can assist you with today?
+     CUSTOMER
+     00:01:40
+     No, that's all. Thank you again.
+     AGENT
+     00:01:45
+     You're welcome. Have a great day.
+     CUSTOMER
+     00:01:49
+     You too."</t>
+  </si>
+  <si>
+    <t>The customer's tone is calm and factual throughout the conversation, with a focus on providing information and resolving the issue. They express gratitude and appreciation for the agent's help, but do not show strong emotions such as joy, sadness, anger, or fear.</t>
+  </si>
+  <si>
+    <t>transcript96</t>
+  </si>
+  <si>
+    <t>The customer reported physical damage to their property due to a pipe burst in the basement, causing water damage. The agent documented the damage with photos and videos, filed a claim, and arranged for an adjuster to assess the damage and start the repair process.</t>
+  </si>
+  <si>
+    <t>The customer is calling to report physical damage to their property and the agent is assisting them with the claim process. The conversation is polite and professional, with no indication of frustration or dissatisfaction that would suggest churn.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon, I'm calling about the battery issue I'm having with my phone. It's been draining really fast and I'm not happy about it.
+     AGENT
+     00:00:15
+     Sorry to hear that. Can you tell me more about the issue you're experiencing? How long has this been going on?
+     CUSTOMER
+     00:00:23
+     It started about a week ago. I've tried restarting it, closing apps, everything. But nothing seems to be working. I'm really frustrated.
+     AGENT
+     00:00:33
+     I understand your frustration. Have you tried calibrating your battery or updating your operating system?
+     CUSTOMER
+     00:00:41
+     Yeah, I've tried all that. Like I said, I've tried everything. I think there's a problem with the battery itself.
+     AGENT
+     00:00:49
+     Okay, I'm going to go ahead and set up a repair order for you. We'll get a new battery sent out to you.
+     CUSTOMER
+     00:00:57
+     That's going to take how long? I need my phone for work.
+     AGENT
+     00:01:03
+     It should take about 3-5 business days to arrive.
+     CUSTOMER
+     00:01:09
+     That's unacceptable. I need it faster than that. Can't you just send someone to fix it today?
+     AGENT
+     00:01:16
+     I apologize, but that's not an option. However, I can offer you a loaner phone in the meantime.
+     CUSTOMER
+     00:01:24
+     A loaner phone? That's not what I want. I want my phone fixed now.
+     AGENT
+     00:01:31
+     I understand, but it's not possible to send someone to fix it today. I can escalate this issue to my supervisor to see what else we can do.
+     CUSTOMER
+     00:01:39
+     Fine, do that. I'm not happy with the service I'm getting.
+     AGENT
+     00:01:45
+     I apologize again for the inconvenience. Let me go ahead and escalate this issue. Can you please hold for just a moment?
+     CUSTOMER
+     00:01:52
+     Yeah, fine.
+     AGENT
+     00:02:00
+     Okay, I've escalated the issue. My supervisor is going to call you within the next 24 hours to discuss further options.
+     CUSTOMER
+     00:02:07
+     24 hours? That's ridiculous. I need it fixed now.
+     AGENT
+     00:02:13
+     I apologize, but that's the best we can do. Is there anything else I can assist you with today?
+     CUSTOMER
+     00:02:19
+     No, that's it. I'm extremely dissatisfied with the service I've received.
+     AGENT
+     00:02:25
+     I apologize again for the inconvenience. We'll do our best to get your issue resolved as soon as possible.
+     CUSTOMER
+     00:02:31
+     Yeah, right. Thanks for nothing.
+     AGENT
+     00:02:36
+     You're welcome. Have a good day.
+     CUSTOMER
+     00:02:40
+     Yeah, right."</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration, annoyance, and strong dissatisfaction throughout the conversation, using phrases like 'I'm not happy about it', 'I'm really frustrated', 'That's unacceptable', 'I'm not happy with the service I'm getting', and 'I'm extremely dissatisfied with the service I've received'. The customer's tone is consistently negative and confrontational, indicating a strong emotional state of anger.</t>
+  </si>
+  <si>
+    <t>transcript97</t>
+  </si>
+  <si>
+    <t>Customer is experiencing a battery issue with their phone, which started a week ago. The customer has tried various troubleshooting steps but is still experiencing the issue. The agent offers to set up a repair order and provides a loaner phone, but the customer is dissatisfied with the service and wants the issue resolved immediately. The agent escalates the issue to their supervisor, who will contact the customer within 24 hours to discuss further options.</t>
+  </si>
+  <si>
+    <t>I'm extremely dissatisfied with the service I've received.</t>
+  </si>
+  <si>
+    <t>The customer is extremely frustrated and dissatisfied with the service, explicitly stating their unhappiness, which suggests a high risk of churn.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon, I'm Joy. I'm having some issues with my laptop. The keyboard is not working properly.
+     AGENT
+     00:00:15
+     Sorry to hear that, Joy. Can you tell me more about the issue you're experiencing with your keyboard? Is it not responding at all or is it intermittent?
+     CUSTOMER
+     00:00:25
+     It's intermittent. Sometimes it works, sometimes it doesn't. And it's really frustrating because I need it for work.
+     AGENT
+     00:00:35
+     I understand how frustrating that must be. Have you tried restarting your laptop or updating your keyboard drivers?
+     CUSTOMER
+     00:00:45
+     Yeah, I've tried restarting, but I'm not sure about the drivers. I'm not very tech-savvy.
+     AGENT
+     00:00:55
+     No worries, Joy. I can walk you through that. But before we do, can you tell me what kind of laptop you have and how old it is?
+     CUSTOMER
+     00:01:05
+     It's a Dell Inspiron, and I think it's about 3 years old.
+     AGENT
+     00:01:15
+     Okay. And have you spilled anything on the keyboard or exposed it to any liquids recently?
+     CUSTOMER
+     00:01:25
+     Actually, yes. I spilled coffee on it a few days ago. But I thought I cleaned it up pretty well.
+     AGENT
+     00:01:35
+     That might be the culprit. Liquid damage can cause all sorts of issues. I'm going to go ahead and send you a link to update your keyboard drivers. Can you try that and see if it resolves the issue?
+     CUSTOMER
+     00:01:45
+     Okay, I'll try it. But what if it doesn't work? I really need my laptop to be working properly.
+     AGENT
+     00:01:55
+     If updating the drivers doesn't work, we can explore other options, such as repairing or replacing the keyboard. We can also discuss possible warranty options if your laptop is still under warranty.
+     CUSTOMER
+     00:02:05
+     Okay, that sounds good. I appreciate your help.
+     AGENT
+     00:02:15
+     You're welcome, Joy. I'm going to go ahead and escalate this issue to our advanced technical support team. They'll be in touch with you within the next 24 hours to further assist you.
+     CUSTOMER
+     00:02:25
+     Okay, thank you. I appreciate it.
+     AGENT
+     00:02:35
+     You're welcome, Joy. Is there anything else I can assist you with today?
+     CUSTOMER
+     00:02:45
+     No, that's all. Thank you again for your help.
+     AGENT
+     00:02:55
+     You're welcome, Joy. Have a great day."</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration and annoyance throughout the conversation, particularly when describing the issue with their keyboard ('It's intermittent. Sometimes it works, sometimes it doesn't. And it's really frustrating because I need it for work.') and when discussing the potential outcome if the issue is not resolved ('But what if it doesn't work? I really need my laptop to be working properly.').</t>
+  </si>
+  <si>
+    <t>transcript98</t>
+  </si>
+  <si>
+    <t>Customer Joy's laptop keyboard is not working properly due to intermittent issues. The agent suspects liquid damage from a coffee spill and recommends updating the keyboard drivers. If that doesn't work, they will explore other options such as repairing or replacing the keyboard and discuss warranty possibilities.</t>
+  </si>
+  <si>
+    <t>The customer is calling about a technical issue with their laptop, and the agent is able to assist them in resolving the issue. The customer's tone is frustrated but not angry, and they do not express any intent to switch companies.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon
+     AGENT
+     00:00:10
+     How can I assist you today?
+     CUSTOMER
+     00:00:15
+     I am having some issues with my internet connection. It's been slow for the past few days.
+     AGENT
+     00:00:22
+     Sorry to hear that. Can you please tell me more about the issue you're experiencing? 
+     CUSTOMER
+     00:00:30
+     Yeah, like I said, it's just been really slow. I've tried restarting my router and modem, but that hasn't helped.
+     AGENT
+     00:00:38
+     Okay, I'm going to go ahead and check on the status of our network in your area. Can you please provide me with your account information so I can look into this further?
+     CUSTOMER
+     00:00:45
+     Yeah, my account number is 123456.
+     AGENT
+     00:00:52
+     Thank you for providing that information. I've checked on the status of our network, and it appears that there is an outage in your area. 
+     CUSTOMER
+     00:01:00
+     An outage? When is it going to be fixed?
+     AGENT
+     00:01:05
+     Our team is working on resolving the issue as soon as possible. I apologize for the inconvenience this has caused. 
+     CUSTOMER
+     00:01:12
+     This is ridiculous. I pay a lot of money for this service, and I expect it to work. 
+     AGENT
+     00:01:18
+     I completely understand, and I apologize again for the issue. I'm going to go ahead and credit your account for the inconvenience. 
+     CUSTOMER
+     00:01:25
+     That's not good enough. I want to speak to a supervisor.
+     AGENT
+     00:01:30
+     I understand, and I'm happy to escalate this issue to my supervisor. Please hold for just a moment. 
+     CUSTOMER
+     00:01:40
+     (sighs) Fine.
+     AGENT
+     00:01:45
+     My supervisor is on the line now. 
+     SUPERVISOR
+     00:01:50
+     Hello, I apologize for the inconvenience you've experienced with your internet connection. I'm happy to help resolve this issue for you."</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration and annoyance throughout the conversation, particularly when discussing the ongoing outage and the lack of satisfactory resolution from the support agent. The customer's language, such as 'This is ridiculous,' 'That's not good enough,' and the audible sigh, indicates a strong emotional tone of anger.</t>
+  </si>
+  <si>
+    <t>transcript99</t>
+  </si>
+  <si>
+    <t>Customer reported slow internet connection due to an outage in their area. Agent checked the network status and apologized for the inconvenience. Customer was dissatisfied and escalated the issue to a supervisor, who offered to help resolve the problem.</t>
+  </si>
+  <si>
+    <t>This is ridiculous. I pay a lot of money for this service, and I expect it to work.</t>
+  </si>
+  <si>
+    <t>Customer is angry and frustrated with the service, and has called before but issue was not resolved, which suggests medium churn.</t>
+  </si>
+  <si>
+    <t>"AGENT
+     00:00:00
+     Hello good afternoon.
+     CUSTOMER
+     00:00:07
+     good afternoon. I'm having some issues with the software. It's been freezing on me every time I try to open a new project.
+     AGENT
+     00:00:15
+     Sorry to hear that. Can you tell me more about the issue you're experiencing? What kind of projects are you trying to open?
+     CUSTOMER
+     00:00:25
+     It's happening with all projects, regardless of size or type. I've tried restarting the program and my computer, but nothing seems to be working.
+     AGENT
+     00:00:35
+     I see. Have you tried updating the software to the latest version? Sometimes that can resolve issues like this.
+     CUSTOMER
+     00:00:45
+     Yeah, I've tried that. I'm running the latest version. I'm starting to get really frustrated with this. I need to get some work done and this is holding me back.
+     AGENT
+     00:00:55
+     I understand your frustration. Let me see what else I can do to help. Can you please provide me with your software license number so I can look into this further?
+     CUSTOMER
+     00:01:05
+     It's #123456. But I'm not sure if I want to continue using this software if it's going to keep causing me problems.
+     AGENT
+     00:01:15
+     I completely understand. I'm going to go ahead and escalate this issue to our advanced technical support team. They'll be able to take a closer look and provide a more detailed solution.
+     CUSTOMER
+     00:01:25
+     Okay... I hope so. I'm not sure how much more of this I can take.
+     AGENT
+     00:01:35
+     I completely understand, and I apologize again for the inconvenience. Our technical support team will be in touch with you within the next 24 hours to resolve this issue.
+     CUSTOMER
+     00:01:45
+     Okay. Thank you, I guess.
+     AGENT
+     00:01:55
+     You're welcome. Is there anything else I can assist you with today?
+     CUSTOMER
+     00:02:05
+     No, that's all. Thanks again.
+     AGENT
+     00:02:15
+     You're welcome. Have a great day.
+     CUSTOMER
+     00:02:25
+     Yeah, you too."</t>
+  </si>
+  <si>
+    <t>The customer expresses frustration and annoyance throughout the conversation, particularly in messages where they mention the software freezing and their need to get work done. They also explicitly state that they're 'getting really frustrated' and 'not sure how much more of this I can take', indicating a strong negative emotional tone.</t>
+  </si>
+  <si>
+    <t>transcript100</t>
+  </si>
+  <si>
+    <t>Customer is experiencing issues with software freezing when opening new projects. Agent tries to troubleshoot the issue, suggests updating the software, and escalates the problem to advanced technical support. Customer is frustrated and hopes for a resolution within 24 hours.</t>
+  </si>
+  <si>
+    <t>I'm not sure if I want to continue using this software if it's going to keep causing me problems.</t>
+  </si>
+  <si>
+    <t>The customer is frustrated with the software and is questioning whether to continue using it, indicating a medium level of churn.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4317,13 +7704,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4361,7 +7756,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4395,6 +7790,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4429,9 +7825,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4604,11 +8001,56 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BM51"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:BM101"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="255.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="255.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="255.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="255.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="86.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="252.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="255.6328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.08984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="198.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="30" max="34" width="3.1796875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="39" max="41" width="2.81640625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="43" max="45" width="4" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="47" max="49" width="4" bestFit="1" customWidth="1"/>
+    <col min="50" max="54" width="3.7265625" bestFit="1" customWidth="1"/>
+    <col min="55" max="58" width="4.6328125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="3.7265625" bestFit="1" customWidth="1"/>
+    <col min="60" max="63" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="64" max="65" width="3.453125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:65">
+    <row r="1" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4805,7 +8247,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:65">
+    <row r="2" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>65</v>
       </c>
@@ -4888,7 +8330,7 @@
         <v>0.35</v>
       </c>
       <c r="AB2">
-        <v>0.6305555555555555</v>
+        <v>0.63055555555555554</v>
       </c>
       <c r="AC2" t="s">
         <v>535</v>
@@ -4930,7 +8372,7 @@
         <v>1</v>
       </c>
       <c r="AP2">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AQ2">
         <v>1</v>
@@ -4942,7 +8384,7 @@
         <v>1</v>
       </c>
       <c r="AT2">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU2">
         <v>1</v>
@@ -5002,7 +8444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:65">
+    <row r="3" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>66</v>
       </c>
@@ -5085,7 +8527,7 @@
         <v>0.24</v>
       </c>
       <c r="AB3">
-        <v>0.5694444444444444</v>
+        <v>0.56944444444444442</v>
       </c>
       <c r="AC3" t="s">
         <v>535</v>
@@ -5139,7 +8581,7 @@
         <v>1</v>
       </c>
       <c r="AT3">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU3">
         <v>1</v>
@@ -5199,7 +8641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:65">
+    <row r="4" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>67</v>
       </c>
@@ -5273,13 +8715,13 @@
         <v>1001</v>
       </c>
       <c r="Z4">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="AA4">
         <v>0.46</v>
       </c>
       <c r="AB4">
-        <v>0.5349999999999999</v>
+        <v>0.53499999999999992</v>
       </c>
       <c r="AC4" t="s">
         <v>535</v>
@@ -5321,7 +8763,7 @@
         <v>1</v>
       </c>
       <c r="AP4">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ4">
         <v>1</v>
@@ -5333,7 +8775,7 @@
         <v>1</v>
       </c>
       <c r="AT4">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU4">
         <v>1</v>
@@ -5393,7 +8835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:65">
+    <row r="5" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>68</v>
       </c>
@@ -5473,7 +8915,7 @@
         <v>0.37</v>
       </c>
       <c r="AB5">
-        <v>0.5533333333333333</v>
+        <v>0.55333333333333334</v>
       </c>
       <c r="AC5" t="s">
         <v>535</v>
@@ -5515,7 +8957,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ5">
         <v>1</v>
@@ -5527,7 +8969,7 @@
         <v>1</v>
       </c>
       <c r="AT5">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU5">
         <v>1</v>
@@ -5587,7 +9029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:65">
+    <row r="6" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>69</v>
       </c>
@@ -5664,13 +9106,13 @@
         <v>1001</v>
       </c>
       <c r="Z6">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="AA6">
         <v>0.13</v>
       </c>
       <c r="AB6">
-        <v>0.6472222222222223</v>
+        <v>0.64722222222222225</v>
       </c>
       <c r="AC6" t="s">
         <v>535</v>
@@ -5712,7 +9154,7 @@
         <v>1</v>
       </c>
       <c r="AP6">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ6">
         <v>1</v>
@@ -5784,7 +9226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:65">
+    <row r="7" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>70</v>
       </c>
@@ -5867,7 +9309,7 @@
         <v>0.38</v>
       </c>
       <c r="AB7">
-        <v>0.5966666666666666</v>
+        <v>0.59666666666666657</v>
       </c>
       <c r="AC7" t="s">
         <v>535</v>
@@ -5909,7 +9351,7 @@
         <v>1</v>
       </c>
       <c r="AP7">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ7">
         <v>1</v>
@@ -5921,7 +9363,7 @@
         <v>1</v>
       </c>
       <c r="AT7">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU7">
         <v>1</v>
@@ -5981,7 +9423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:65">
+    <row r="8" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>71</v>
       </c>
@@ -6064,7 +9506,7 @@
         <v>0.24</v>
       </c>
       <c r="AB8">
-        <v>0.615</v>
+        <v>0.61499999999999999</v>
       </c>
       <c r="AC8" t="s">
         <v>535</v>
@@ -6106,7 +9548,7 @@
         <v>1</v>
       </c>
       <c r="AP8">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ8">
         <v>1</v>
@@ -6118,7 +9560,7 @@
         <v>1</v>
       </c>
       <c r="AT8">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU8">
         <v>1</v>
@@ -6178,7 +9620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:65">
+    <row r="9" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>72</v>
       </c>
@@ -6252,13 +9694,13 @@
         <v>1000</v>
       </c>
       <c r="Z9">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="AA9">
         <v>0.5</v>
       </c>
       <c r="AB9">
-        <v>0.4949999999999999</v>
+        <v>0.49499999999999988</v>
       </c>
       <c r="AC9" t="s">
         <v>536</v>
@@ -6300,7 +9742,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -6312,7 +9754,7 @@
         <v>1</v>
       </c>
       <c r="AT9">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU9">
         <v>1</v>
@@ -6372,7 +9814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:65">
+    <row r="10" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>73</v>
       </c>
@@ -6452,7 +9894,7 @@
         <v>0.2</v>
       </c>
       <c r="AB10">
-        <v>0.6266666666666666</v>
+        <v>0.62666666666666659</v>
       </c>
       <c r="AC10" t="s">
         <v>535</v>
@@ -6494,7 +9936,7 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ10">
         <v>1</v>
@@ -6506,7 +9948,7 @@
         <v>1</v>
       </c>
       <c r="AT10">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU10">
         <v>1</v>
@@ -6566,7 +10008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:65">
+    <row r="11" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>74</v>
       </c>
@@ -6643,13 +10085,13 @@
         <v>1000</v>
       </c>
       <c r="Z11">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="AA11">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AB11">
-        <v>0.7222222222222222</v>
+        <v>0.72222222222222221</v>
       </c>
       <c r="AC11" t="s">
         <v>537</v>
@@ -6691,7 +10133,7 @@
         <v>1</v>
       </c>
       <c r="AP11">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AQ11">
         <v>1</v>
@@ -6703,7 +10145,7 @@
         <v>1</v>
       </c>
       <c r="AT11">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU11">
         <v>1</v>
@@ -6763,7 +10205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:65">
+    <row r="12" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>75</v>
       </c>
@@ -6837,13 +10279,13 @@
         <v>1000</v>
       </c>
       <c r="Z12">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="AA12">
         <v>0.37</v>
       </c>
       <c r="AB12">
-        <v>0.4961111111111111</v>
+        <v>0.49611111111111111</v>
       </c>
       <c r="AC12" t="s">
         <v>536</v>
@@ -6897,7 +10339,7 @@
         <v>1</v>
       </c>
       <c r="AT12">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU12">
         <v>1</v>
@@ -6957,7 +10399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:65">
+    <row r="13" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>76</v>
       </c>
@@ -7040,7 +10482,7 @@
         <v>0.5</v>
       </c>
       <c r="AB13">
-        <v>0.5383333333333333</v>
+        <v>0.53833333333333333</v>
       </c>
       <c r="AC13" t="s">
         <v>535</v>
@@ -7082,7 +10524,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ13">
         <v>1</v>
@@ -7094,7 +10536,7 @@
         <v>1</v>
       </c>
       <c r="AT13">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU13">
         <v>1</v>
@@ -7154,7 +10596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:65">
+    <row r="14" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>77</v>
       </c>
@@ -7231,13 +10673,13 @@
         <v>1000</v>
       </c>
       <c r="Z14">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="AA14">
         <v>0.34</v>
       </c>
       <c r="AB14">
-        <v>0.6938888888888889</v>
+        <v>0.69388888888888889</v>
       </c>
       <c r="AC14" t="s">
         <v>535</v>
@@ -7279,7 +10721,7 @@
         <v>1</v>
       </c>
       <c r="AP14">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AQ14">
         <v>1</v>
@@ -7291,7 +10733,7 @@
         <v>1</v>
       </c>
       <c r="AT14">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU14">
         <v>1</v>
@@ -7351,7 +10793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:65">
+    <row r="15" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>78</v>
       </c>
@@ -7434,7 +10876,7 @@
         <v>0.16</v>
       </c>
       <c r="AB15">
-        <v>0.7394444444444446</v>
+        <v>0.73944444444444457</v>
       </c>
       <c r="AC15" t="s">
         <v>537</v>
@@ -7476,7 +10918,7 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -7548,7 +10990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:65">
+    <row r="16" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>79</v>
       </c>
@@ -7622,7 +11064,7 @@
         <v>1001</v>
       </c>
       <c r="Z16">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="AA16">
         <v>0.49</v>
@@ -7670,7 +11112,7 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ16">
         <v>1</v>
@@ -7742,7 +11184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:65">
+    <row r="17" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>80</v>
       </c>
@@ -7819,10 +11261,10 @@
         <v>0.61</v>
       </c>
       <c r="AA17">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AB17">
-        <v>0.6272222222222222</v>
+        <v>0.62722222222222224</v>
       </c>
       <c r="AC17" t="s">
         <v>535</v>
@@ -7864,7 +11306,7 @@
         <v>1</v>
       </c>
       <c r="AP17">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ17">
         <v>1</v>
@@ -7936,7 +11378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:65">
+    <row r="18" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>81</v>
       </c>
@@ -8019,7 +11461,7 @@
         <v>0.37</v>
       </c>
       <c r="AB18">
-        <v>0.5583333333333332</v>
+        <v>0.55833333333333324</v>
       </c>
       <c r="AC18" t="s">
         <v>535</v>
@@ -8061,7 +11503,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ18">
         <v>1</v>
@@ -8073,7 +11515,7 @@
         <v>1</v>
       </c>
       <c r="AT18">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU18">
         <v>1</v>
@@ -8133,7 +11575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:65">
+    <row r="19" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>82</v>
       </c>
@@ -8216,7 +11658,7 @@
         <v>0.15</v>
       </c>
       <c r="AB19">
-        <v>0.6838888888888889</v>
+        <v>0.68388888888888888</v>
       </c>
       <c r="AC19" t="s">
         <v>535</v>
@@ -8258,7 +11700,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -8330,7 +11772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:65">
+    <row r="20" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>83</v>
       </c>
@@ -8410,7 +11852,7 @@
         <v>0.38</v>
       </c>
       <c r="AB20">
-        <v>0.5983333333333333</v>
+        <v>0.59833333333333327</v>
       </c>
       <c r="AC20" t="s">
         <v>535</v>
@@ -8452,7 +11894,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ20">
         <v>1</v>
@@ -8464,7 +11906,7 @@
         <v>1</v>
       </c>
       <c r="AT20">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU20">
         <v>1</v>
@@ -8524,7 +11966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:65">
+    <row r="21" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>84</v>
       </c>
@@ -8604,7 +12046,7 @@
         <v>0.39</v>
       </c>
       <c r="AB21">
-        <v>0.6788888888888889</v>
+        <v>0.67888888888888888</v>
       </c>
       <c r="AC21" t="s">
         <v>535</v>
@@ -8646,7 +12088,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AQ21">
         <v>1</v>
@@ -8658,7 +12100,7 @@
         <v>1</v>
       </c>
       <c r="AT21">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU21">
         <v>1</v>
@@ -8718,7 +12160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:65">
+    <row r="22" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>85</v>
       </c>
@@ -8798,7 +12240,7 @@
         <v>0.35</v>
       </c>
       <c r="AB22">
-        <v>0.6305555555555555</v>
+        <v>0.63055555555555554</v>
       </c>
       <c r="AC22" t="s">
         <v>535</v>
@@ -8840,7 +12282,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AQ22">
         <v>1</v>
@@ -8852,7 +12294,7 @@
         <v>1</v>
       </c>
       <c r="AT22">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU22">
         <v>1</v>
@@ -8912,7 +12354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:65">
+    <row r="23" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>86</v>
       </c>
@@ -8992,7 +12434,7 @@
         <v>0.24</v>
       </c>
       <c r="AB23">
-        <v>0.5694444444444444</v>
+        <v>0.56944444444444442</v>
       </c>
       <c r="AC23" t="s">
         <v>535</v>
@@ -9046,7 +12488,7 @@
         <v>1</v>
       </c>
       <c r="AT23">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU23">
         <v>1</v>
@@ -9106,7 +12548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:65">
+    <row r="24" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>87</v>
       </c>
@@ -9180,13 +12622,13 @@
         <v>1001</v>
       </c>
       <c r="Z24">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="AA24">
         <v>0.46</v>
       </c>
       <c r="AB24">
-        <v>0.5349999999999999</v>
+        <v>0.53499999999999992</v>
       </c>
       <c r="AC24" t="s">
         <v>535</v>
@@ -9228,7 +12670,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ24">
         <v>1</v>
@@ -9240,7 +12682,7 @@
         <v>1</v>
       </c>
       <c r="AT24">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU24">
         <v>1</v>
@@ -9300,7 +12742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:65">
+    <row r="25" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>88</v>
       </c>
@@ -9380,7 +12822,7 @@
         <v>0.37</v>
       </c>
       <c r="AB25">
-        <v>0.5533333333333333</v>
+        <v>0.55333333333333334</v>
       </c>
       <c r="AC25" t="s">
         <v>535</v>
@@ -9422,7 +12864,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ25">
         <v>1</v>
@@ -9434,7 +12876,7 @@
         <v>1</v>
       </c>
       <c r="AT25">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU25">
         <v>1</v>
@@ -9494,7 +12936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:65">
+    <row r="26" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>89</v>
       </c>
@@ -9571,13 +13013,13 @@
         <v>1001</v>
       </c>
       <c r="Z26">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="AA26">
         <v>0.13</v>
       </c>
       <c r="AB26">
-        <v>0.6472222222222223</v>
+        <v>0.64722222222222225</v>
       </c>
       <c r="AC26" t="s">
         <v>535</v>
@@ -9619,7 +13061,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ26">
         <v>1</v>
@@ -9691,7 +13133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:65">
+    <row r="27" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>90</v>
       </c>
@@ -9774,7 +13216,7 @@
         <v>0.38</v>
       </c>
       <c r="AB27">
-        <v>0.5966666666666666</v>
+        <v>0.59666666666666657</v>
       </c>
       <c r="AC27" t="s">
         <v>535</v>
@@ -9816,7 +13258,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -9828,7 +13270,7 @@
         <v>1</v>
       </c>
       <c r="AT27">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU27">
         <v>1</v>
@@ -9888,7 +13330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:65">
+    <row r="28" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>91</v>
       </c>
@@ -9971,7 +13413,7 @@
         <v>0.24</v>
       </c>
       <c r="AB28">
-        <v>0.615</v>
+        <v>0.61499999999999999</v>
       </c>
       <c r="AC28" t="s">
         <v>535</v>
@@ -10013,7 +13455,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ28">
         <v>1</v>
@@ -10025,7 +13467,7 @@
         <v>1</v>
       </c>
       <c r="AT28">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU28">
         <v>1</v>
@@ -10085,7 +13527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:65">
+    <row r="29" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>92</v>
       </c>
@@ -10159,13 +13601,13 @@
         <v>1000</v>
       </c>
       <c r="Z29">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="AA29">
         <v>0.5</v>
       </c>
       <c r="AB29">
-        <v>0.4949999999999999</v>
+        <v>0.49499999999999988</v>
       </c>
       <c r="AC29" t="s">
         <v>536</v>
@@ -10207,7 +13649,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ29">
         <v>1</v>
@@ -10219,7 +13661,7 @@
         <v>1</v>
       </c>
       <c r="AT29">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU29">
         <v>1</v>
@@ -10279,7 +13721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:65">
+    <row r="30" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>93</v>
       </c>
@@ -10362,7 +13804,7 @@
         <v>0.2</v>
       </c>
       <c r="AB30">
-        <v>0.6266666666666666</v>
+        <v>0.62666666666666659</v>
       </c>
       <c r="AC30" t="s">
         <v>535</v>
@@ -10404,7 +13846,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ30">
         <v>1</v>
@@ -10416,7 +13858,7 @@
         <v>1</v>
       </c>
       <c r="AT30">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU30">
         <v>1</v>
@@ -10476,7 +13918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:65">
+    <row r="31" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>94</v>
       </c>
@@ -10550,13 +13992,13 @@
         <v>1000</v>
       </c>
       <c r="Z31">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="AA31">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AB31">
-        <v>0.7222222222222222</v>
+        <v>0.72222222222222221</v>
       </c>
       <c r="AC31" t="s">
         <v>537</v>
@@ -10598,7 +14040,7 @@
         <v>1</v>
       </c>
       <c r="AP31">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AQ31">
         <v>1</v>
@@ -10610,7 +14052,7 @@
         <v>1</v>
       </c>
       <c r="AT31">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU31">
         <v>1</v>
@@ -10670,7 +14112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:65">
+    <row r="32" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>95</v>
       </c>
@@ -10741,13 +14183,13 @@
         <v>1000</v>
       </c>
       <c r="Z32">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="AA32">
         <v>0.37</v>
       </c>
       <c r="AB32">
-        <v>0.4961111111111111</v>
+        <v>0.49611111111111111</v>
       </c>
       <c r="AC32" t="s">
         <v>536</v>
@@ -10801,7 +14243,7 @@
         <v>1</v>
       </c>
       <c r="AT32">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU32">
         <v>1</v>
@@ -10861,7 +14303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:65">
+    <row r="33" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>96</v>
       </c>
@@ -10944,7 +14386,7 @@
         <v>0.5</v>
       </c>
       <c r="AB33">
-        <v>0.5383333333333333</v>
+        <v>0.53833333333333333</v>
       </c>
       <c r="AC33" t="s">
         <v>535</v>
@@ -10986,7 +14428,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ33">
         <v>1</v>
@@ -10998,7 +14440,7 @@
         <v>1</v>
       </c>
       <c r="AT33">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU33">
         <v>1</v>
@@ -11058,7 +14500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:65">
+    <row r="34" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>97</v>
       </c>
@@ -11132,13 +14574,13 @@
         <v>1000</v>
       </c>
       <c r="Z34">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="AA34">
         <v>0.34</v>
       </c>
       <c r="AB34">
-        <v>0.6938888888888889</v>
+        <v>0.69388888888888889</v>
       </c>
       <c r="AC34" t="s">
         <v>535</v>
@@ -11180,7 +14622,7 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AQ34">
         <v>1</v>
@@ -11192,7 +14634,7 @@
         <v>1</v>
       </c>
       <c r="AT34">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU34">
         <v>1</v>
@@ -11252,7 +14694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:65">
+    <row r="35" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>98</v>
       </c>
@@ -11335,7 +14777,7 @@
         <v>0.16</v>
       </c>
       <c r="AB35">
-        <v>0.7394444444444446</v>
+        <v>0.73944444444444457</v>
       </c>
       <c r="AC35" t="s">
         <v>537</v>
@@ -11377,7 +14819,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AQ35">
         <v>1</v>
@@ -11449,7 +14891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:65">
+    <row r="36" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>99</v>
       </c>
@@ -11526,7 +14968,7 @@
         <v>1001</v>
       </c>
       <c r="Z36">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="AA36">
         <v>0.49</v>
@@ -11574,7 +15016,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ36">
         <v>1</v>
@@ -11646,7 +15088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:65">
+    <row r="37" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>100</v>
       </c>
@@ -11723,10 +15165,10 @@
         <v>0.61</v>
       </c>
       <c r="AA37">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AB37">
-        <v>0.6272222222222222</v>
+        <v>0.62722222222222224</v>
       </c>
       <c r="AC37" t="s">
         <v>535</v>
@@ -11768,7 +15210,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ37">
         <v>1</v>
@@ -11840,7 +15282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:65">
+    <row r="38" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>101</v>
       </c>
@@ -11920,7 +15362,7 @@
         <v>0.37</v>
       </c>
       <c r="AB38">
-        <v>0.5583333333333332</v>
+        <v>0.55833333333333324</v>
       </c>
       <c r="AC38" t="s">
         <v>535</v>
@@ -11962,7 +15404,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ38">
         <v>1</v>
@@ -11974,7 +15416,7 @@
         <v>1</v>
       </c>
       <c r="AT38">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU38">
         <v>1</v>
@@ -12034,7 +15476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:65">
+    <row r="39" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>102</v>
       </c>
@@ -12114,7 +15556,7 @@
         <v>0.15</v>
       </c>
       <c r="AB39">
-        <v>0.6838888888888889</v>
+        <v>0.68388888888888888</v>
       </c>
       <c r="AC39" t="s">
         <v>535</v>
@@ -12156,7 +15598,7 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ39">
         <v>1</v>
@@ -12228,7 +15670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:65">
+    <row r="40" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>103</v>
       </c>
@@ -12308,7 +15750,7 @@
         <v>0.38</v>
       </c>
       <c r="AB40">
-        <v>0.5983333333333333</v>
+        <v>0.59833333333333327</v>
       </c>
       <c r="AC40" t="s">
         <v>535</v>
@@ -12350,7 +15792,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ40">
         <v>1</v>
@@ -12362,7 +15804,7 @@
         <v>1</v>
       </c>
       <c r="AT40">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU40">
         <v>1</v>
@@ -12422,7 +15864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:65">
+    <row r="41" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>104</v>
       </c>
@@ -12505,7 +15947,7 @@
         <v>0.39</v>
       </c>
       <c r="AB41">
-        <v>0.6788888888888889</v>
+        <v>0.67888888888888888</v>
       </c>
       <c r="AC41" t="s">
         <v>535</v>
@@ -12547,7 +15989,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AQ41">
         <v>1</v>
@@ -12559,7 +16001,7 @@
         <v>1</v>
       </c>
       <c r="AT41">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU41">
         <v>1</v>
@@ -12619,7 +16061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:65">
+    <row r="42" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>105</v>
       </c>
@@ -12699,7 +16141,7 @@
         <v>0.37</v>
       </c>
       <c r="AB42">
-        <v>0.7727777777777778</v>
+        <v>0.77277777777777779</v>
       </c>
       <c r="AC42" t="s">
         <v>537</v>
@@ -12741,7 +16183,7 @@
         <v>1</v>
       </c>
       <c r="AP42">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AQ42">
         <v>1</v>
@@ -12813,7 +16255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:65">
+    <row r="43" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>106</v>
       </c>
@@ -12896,7 +16338,7 @@
         <v>0.3</v>
       </c>
       <c r="AB43">
-        <v>0.638888889</v>
+        <v>0.63888888899999996</v>
       </c>
       <c r="AC43" t="s">
         <v>535</v>
@@ -12938,7 +16380,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AQ43">
         <v>1</v>
@@ -12950,7 +16392,7 @@
         <v>1</v>
       </c>
       <c r="AT43">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU43">
         <v>1</v>
@@ -13010,7 +16452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:65">
+    <row r="44" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>107</v>
       </c>
@@ -13084,13 +16526,13 @@
         <v>1001</v>
       </c>
       <c r="Z44">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="AA44">
         <v>0.27</v>
       </c>
       <c r="AB44">
-        <v>0.6566666666666666</v>
+        <v>0.65666666666666662</v>
       </c>
       <c r="AC44" t="s">
         <v>535</v>
@@ -13132,7 +16574,7 @@
         <v>1</v>
       </c>
       <c r="AP44">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AQ44">
         <v>1</v>
@@ -13144,7 +16586,7 @@
         <v>1</v>
       </c>
       <c r="AT44">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU44">
         <v>1</v>
@@ -13204,7 +16646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:65">
+    <row r="45" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>108</v>
       </c>
@@ -13281,13 +16723,13 @@
         <v>1001</v>
       </c>
       <c r="Z45">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AA45">
         <v>0.15</v>
       </c>
       <c r="AB45">
-        <v>0.5777777777777778</v>
+        <v>0.57777777777777783</v>
       </c>
       <c r="AC45" t="s">
         <v>535</v>
@@ -13341,7 +16783,7 @@
         <v>1</v>
       </c>
       <c r="AT45">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU45">
         <v>1</v>
@@ -13401,7 +16843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:65">
+    <row r="46" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>109</v>
       </c>
@@ -13523,7 +16965,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AQ46">
         <v>1</v>
@@ -13595,7 +17037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:65">
+    <row r="47" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>110</v>
       </c>
@@ -13678,7 +17120,7 @@
         <v>0.39</v>
       </c>
       <c r="AB47">
-        <v>0.4216666666666666</v>
+        <v>0.42166666666666658</v>
       </c>
       <c r="AC47" t="s">
         <v>536</v>
@@ -13720,7 +17162,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AQ47">
         <v>0</v>
@@ -13732,7 +17174,7 @@
         <v>1</v>
       </c>
       <c r="AT47">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AU47">
         <v>1</v>
@@ -13792,7 +17234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:65">
+    <row r="48" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>111</v>
       </c>
@@ -13869,13 +17311,13 @@
         <v>1001</v>
       </c>
       <c r="Z48">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AA48">
         <v>0.17</v>
       </c>
       <c r="AB48">
-        <v>0.7744444444444444</v>
+        <v>0.77444444444444438</v>
       </c>
       <c r="AC48" t="s">
         <v>537</v>
@@ -13917,7 +17359,7 @@
         <v>1</v>
       </c>
       <c r="AP48">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AQ48">
         <v>1</v>
@@ -13989,7 +17431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:65">
+    <row r="49" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>112</v>
       </c>
@@ -14072,7 +17514,7 @@
         <v>0.12</v>
       </c>
       <c r="AB49">
-        <v>0.6077777777777778</v>
+        <v>0.60777777777777775</v>
       </c>
       <c r="AC49" t="s">
         <v>535</v>
@@ -14126,7 +17568,7 @@
         <v>1</v>
       </c>
       <c r="AT49">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU49">
         <v>1</v>
@@ -14186,7 +17628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:65">
+    <row r="50" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>113</v>
       </c>
@@ -14269,7 +17711,7 @@
         <v>0.35</v>
       </c>
       <c r="AB50">
-        <v>0.6305555555555555</v>
+        <v>0.63055555555555554</v>
       </c>
       <c r="AC50" t="s">
         <v>535</v>
@@ -14311,7 +17753,7 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -14323,7 +17765,7 @@
         <v>1</v>
       </c>
       <c r="AT50">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU50">
         <v>1</v>
@@ -14383,7 +17825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:65">
+    <row r="51" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>114</v>
       </c>
@@ -14460,7 +17902,7 @@
         <v>0.24</v>
       </c>
       <c r="AB51">
-        <v>0.5694444444444444</v>
+        <v>0.56944444444444442</v>
       </c>
       <c r="AC51" t="s">
         <v>535</v>
@@ -14514,7 +17956,7 @@
         <v>1</v>
       </c>
       <c r="AT51">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AU51">
         <v>1</v>
@@ -14572,6 +18014,1540 @@
       </c>
       <c r="BM51">
         <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:65" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>538</v>
+      </c>
+      <c r="B52" t="s">
+        <v>539</v>
+      </c>
+      <c r="C52" t="s">
+        <v>540</v>
+      </c>
+      <c r="D52" t="s">
+        <v>541</v>
+      </c>
+      <c r="E52" t="s">
+        <v>542</v>
+      </c>
+      <c r="F52" t="s">
+        <v>263</v>
+      </c>
+      <c r="G52" t="s">
+        <v>538</v>
+      </c>
+      <c r="H52" t="s">
+        <v>265</v>
+      </c>
+      <c r="I52" t="s">
+        <v>543</v>
+      </c>
+      <c r="J52" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="53" spans="1:65" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>545</v>
+      </c>
+      <c r="B53" t="s">
+        <v>546</v>
+      </c>
+      <c r="C53" t="s">
+        <v>547</v>
+      </c>
+      <c r="D53" t="s">
+        <v>548</v>
+      </c>
+      <c r="E53" t="s">
+        <v>549</v>
+      </c>
+      <c r="F53" t="s">
+        <v>262</v>
+      </c>
+      <c r="G53" t="s">
+        <v>545</v>
+      </c>
+      <c r="H53" t="s">
+        <v>267</v>
+      </c>
+      <c r="J53" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="54" spans="1:65" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>551</v>
+      </c>
+      <c r="B54" t="s">
+        <v>546</v>
+      </c>
+      <c r="C54" t="s">
+        <v>552</v>
+      </c>
+      <c r="D54" t="s">
+        <v>553</v>
+      </c>
+      <c r="E54" t="s">
+        <v>554</v>
+      </c>
+      <c r="F54" t="s">
+        <v>263</v>
+      </c>
+      <c r="G54" t="s">
+        <v>551</v>
+      </c>
+      <c r="H54" t="s">
+        <v>265</v>
+      </c>
+      <c r="I54" t="s">
+        <v>555</v>
+      </c>
+      <c r="J54" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="55" spans="1:65" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>557</v>
+      </c>
+      <c r="B55" t="s">
+        <v>546</v>
+      </c>
+      <c r="C55" t="s">
+        <v>558</v>
+      </c>
+      <c r="D55" t="s">
+        <v>559</v>
+      </c>
+      <c r="E55" t="s">
+        <v>560</v>
+      </c>
+      <c r="F55" t="s">
+        <v>260</v>
+      </c>
+      <c r="G55" t="s">
+        <v>557</v>
+      </c>
+      <c r="H55" t="s">
+        <v>267</v>
+      </c>
+      <c r="J55" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="56" spans="1:65" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>561</v>
+      </c>
+      <c r="B56" t="s">
+        <v>546</v>
+      </c>
+      <c r="C56" t="s">
+        <v>562</v>
+      </c>
+      <c r="D56" t="s">
+        <v>563</v>
+      </c>
+      <c r="E56" t="s">
+        <v>564</v>
+      </c>
+      <c r="F56" t="s">
+        <v>263</v>
+      </c>
+      <c r="G56" t="s">
+        <v>561</v>
+      </c>
+      <c r="H56" t="s">
+        <v>265</v>
+      </c>
+      <c r="I56" t="s">
+        <v>565</v>
+      </c>
+      <c r="J56" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="57" spans="1:65" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>567</v>
+      </c>
+      <c r="B57" t="s">
+        <v>539</v>
+      </c>
+      <c r="C57" t="s">
+        <v>568</v>
+      </c>
+      <c r="D57" t="s">
+        <v>569</v>
+      </c>
+      <c r="E57" t="s">
+        <v>570</v>
+      </c>
+      <c r="F57" t="s">
+        <v>263</v>
+      </c>
+      <c r="G57" t="s">
+        <v>567</v>
+      </c>
+      <c r="H57" t="s">
+        <v>267</v>
+      </c>
+      <c r="J57" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="58" spans="1:65" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>572</v>
+      </c>
+      <c r="B58">
+        <v>8.5</v>
+      </c>
+      <c r="C58" t="s">
+        <v>573</v>
+      </c>
+      <c r="D58" t="s">
+        <v>574</v>
+      </c>
+      <c r="F58" t="s">
+        <v>263</v>
+      </c>
+      <c r="G58" t="s">
+        <v>572</v>
+      </c>
+      <c r="H58" t="s">
+        <v>267</v>
+      </c>
+      <c r="J58" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="59" spans="1:65" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>576</v>
+      </c>
+      <c r="B59" t="s">
+        <v>539</v>
+      </c>
+      <c r="C59" t="s">
+        <v>577</v>
+      </c>
+      <c r="D59" t="s">
+        <v>578</v>
+      </c>
+      <c r="E59" t="s">
+        <v>579</v>
+      </c>
+      <c r="F59" t="s">
+        <v>262</v>
+      </c>
+      <c r="G59" t="s">
+        <v>576</v>
+      </c>
+      <c r="H59" t="s">
+        <v>265</v>
+      </c>
+      <c r="I59" t="s">
+        <v>580</v>
+      </c>
+      <c r="J59" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="60" spans="1:65" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>582</v>
+      </c>
+      <c r="B60" t="s">
+        <v>546</v>
+      </c>
+      <c r="C60" t="s">
+        <v>583</v>
+      </c>
+      <c r="D60" t="s">
+        <v>584</v>
+      </c>
+      <c r="E60" t="s">
+        <v>585</v>
+      </c>
+      <c r="F60" t="s">
+        <v>262</v>
+      </c>
+      <c r="G60" t="s">
+        <v>582</v>
+      </c>
+      <c r="H60" t="s">
+        <v>265</v>
+      </c>
+      <c r="I60" t="s">
+        <v>586</v>
+      </c>
+      <c r="J60" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="61" spans="1:65" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>588</v>
+      </c>
+      <c r="B61" t="s">
+        <v>546</v>
+      </c>
+      <c r="C61" t="s">
+        <v>589</v>
+      </c>
+      <c r="D61" t="s">
+        <v>590</v>
+      </c>
+      <c r="E61" t="s">
+        <v>591</v>
+      </c>
+      <c r="F61" t="s">
+        <v>262</v>
+      </c>
+      <c r="G61" t="s">
+        <v>588</v>
+      </c>
+      <c r="H61" t="s">
+        <v>265</v>
+      </c>
+      <c r="I61" t="s">
+        <v>592</v>
+      </c>
+      <c r="J61" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="62" spans="1:65" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>594</v>
+      </c>
+      <c r="B62">
+        <v>8</v>
+      </c>
+      <c r="C62" t="s">
+        <v>595</v>
+      </c>
+      <c r="D62" t="s">
+        <v>596</v>
+      </c>
+      <c r="E62" t="s">
+        <v>597</v>
+      </c>
+      <c r="F62" t="s">
+        <v>263</v>
+      </c>
+      <c r="G62" t="s">
+        <v>594</v>
+      </c>
+      <c r="H62" t="s">
+        <v>267</v>
+      </c>
+      <c r="I62" t="s">
+        <v>598</v>
+      </c>
+      <c r="J62" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="63" spans="1:65" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>600</v>
+      </c>
+      <c r="B63" t="s">
+        <v>601</v>
+      </c>
+      <c r="C63" t="s">
+        <v>602</v>
+      </c>
+      <c r="D63" t="s">
+        <v>603</v>
+      </c>
+      <c r="E63" t="s">
+        <v>604</v>
+      </c>
+      <c r="F63" t="s">
+        <v>262</v>
+      </c>
+      <c r="G63" t="s">
+        <v>600</v>
+      </c>
+      <c r="H63" t="s">
+        <v>268</v>
+      </c>
+      <c r="I63" t="s">
+        <v>605</v>
+      </c>
+      <c r="J63" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="64" spans="1:65" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>607</v>
+      </c>
+      <c r="B64" t="s">
+        <v>539</v>
+      </c>
+      <c r="C64" t="s">
+        <v>608</v>
+      </c>
+      <c r="D64" t="s">
+        <v>609</v>
+      </c>
+      <c r="E64" t="s">
+        <v>610</v>
+      </c>
+      <c r="F64" t="s">
+        <v>262</v>
+      </c>
+      <c r="G64" t="s">
+        <v>607</v>
+      </c>
+      <c r="H64" t="s">
+        <v>265</v>
+      </c>
+      <c r="I64" t="s">
+        <v>611</v>
+      </c>
+      <c r="J64" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>613</v>
+      </c>
+      <c r="B65" t="s">
+        <v>539</v>
+      </c>
+      <c r="C65" t="s">
+        <v>614</v>
+      </c>
+      <c r="D65" t="s">
+        <v>615</v>
+      </c>
+      <c r="E65" t="s">
+        <v>616</v>
+      </c>
+      <c r="F65" t="s">
+        <v>262</v>
+      </c>
+      <c r="G65" t="s">
+        <v>613</v>
+      </c>
+      <c r="H65" t="s">
+        <v>265</v>
+      </c>
+      <c r="I65" t="s">
+        <v>617</v>
+      </c>
+      <c r="J65" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>619</v>
+      </c>
+      <c r="B66" t="s">
+        <v>546</v>
+      </c>
+      <c r="C66" t="s">
+        <v>620</v>
+      </c>
+      <c r="D66" t="s">
+        <v>621</v>
+      </c>
+      <c r="E66" t="s">
+        <v>622</v>
+      </c>
+      <c r="F66" t="s">
+        <v>263</v>
+      </c>
+      <c r="G66" t="s">
+        <v>619</v>
+      </c>
+      <c r="H66" t="s">
+        <v>265</v>
+      </c>
+      <c r="I66" t="s">
+        <v>271</v>
+      </c>
+      <c r="J66" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>624</v>
+      </c>
+      <c r="B67" t="s">
+        <v>539</v>
+      </c>
+      <c r="C67" t="s">
+        <v>625</v>
+      </c>
+      <c r="D67" t="s">
+        <v>626</v>
+      </c>
+      <c r="E67" t="s">
+        <v>627</v>
+      </c>
+      <c r="F67" t="s">
+        <v>262</v>
+      </c>
+      <c r="G67" t="s">
+        <v>624</v>
+      </c>
+      <c r="H67" t="s">
+        <v>265</v>
+      </c>
+      <c r="I67" t="s">
+        <v>628</v>
+      </c>
+      <c r="J67" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>630</v>
+      </c>
+      <c r="B68" t="s">
+        <v>546</v>
+      </c>
+      <c r="C68" t="s">
+        <v>631</v>
+      </c>
+      <c r="D68" t="s">
+        <v>632</v>
+      </c>
+      <c r="E68" t="s">
+        <v>633</v>
+      </c>
+      <c r="F68" t="s">
+        <v>262</v>
+      </c>
+      <c r="G68" t="s">
+        <v>630</v>
+      </c>
+      <c r="H68" t="s">
+        <v>265</v>
+      </c>
+      <c r="I68" t="s">
+        <v>634</v>
+      </c>
+      <c r="J68" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>636</v>
+      </c>
+      <c r="B69" t="s">
+        <v>601</v>
+      </c>
+      <c r="C69" t="s">
+        <v>637</v>
+      </c>
+      <c r="D69" t="s">
+        <v>638</v>
+      </c>
+      <c r="E69" t="s">
+        <v>639</v>
+      </c>
+      <c r="F69" t="s">
+        <v>262</v>
+      </c>
+      <c r="G69" t="s">
+        <v>636</v>
+      </c>
+      <c r="H69" t="s">
+        <v>265</v>
+      </c>
+      <c r="I69" t="s">
+        <v>640</v>
+      </c>
+      <c r="J69" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>642</v>
+      </c>
+      <c r="B70" t="s">
+        <v>643</v>
+      </c>
+      <c r="C70" t="s">
+        <v>644</v>
+      </c>
+      <c r="D70" t="s">
+        <v>645</v>
+      </c>
+      <c r="E70" t="s">
+        <v>646</v>
+      </c>
+      <c r="F70" t="s">
+        <v>260</v>
+      </c>
+      <c r="G70" t="s">
+        <v>642</v>
+      </c>
+      <c r="H70" t="s">
+        <v>267</v>
+      </c>
+      <c r="J70" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>648</v>
+      </c>
+      <c r="B71" t="s">
+        <v>649</v>
+      </c>
+      <c r="C71" t="s">
+        <v>650</v>
+      </c>
+      <c r="D71" t="s">
+        <v>651</v>
+      </c>
+      <c r="E71" t="s">
+        <v>652</v>
+      </c>
+      <c r="F71" t="s">
+        <v>262</v>
+      </c>
+      <c r="G71" t="s">
+        <v>648</v>
+      </c>
+      <c r="H71" t="s">
+        <v>268</v>
+      </c>
+      <c r="I71" t="s">
+        <v>653</v>
+      </c>
+      <c r="J71" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>654</v>
+      </c>
+      <c r="B72" t="s">
+        <v>546</v>
+      </c>
+      <c r="C72" t="s">
+        <v>655</v>
+      </c>
+      <c r="D72" t="s">
+        <v>656</v>
+      </c>
+      <c r="E72" t="s">
+        <v>657</v>
+      </c>
+      <c r="F72" t="s">
+        <v>262</v>
+      </c>
+      <c r="G72" t="s">
+        <v>654</v>
+      </c>
+      <c r="H72" t="s">
+        <v>265</v>
+      </c>
+      <c r="I72" t="s">
+        <v>592</v>
+      </c>
+      <c r="J72" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>659</v>
+      </c>
+      <c r="B73" t="s">
+        <v>546</v>
+      </c>
+      <c r="C73" t="s">
+        <v>660</v>
+      </c>
+      <c r="D73" t="s">
+        <v>661</v>
+      </c>
+      <c r="E73" t="s">
+        <v>662</v>
+      </c>
+      <c r="F73" t="s">
+        <v>263</v>
+      </c>
+      <c r="G73" t="s">
+        <v>659</v>
+      </c>
+      <c r="H73" t="s">
+        <v>267</v>
+      </c>
+      <c r="J73" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>664</v>
+      </c>
+      <c r="B74" t="s">
+        <v>539</v>
+      </c>
+      <c r="C74" t="s">
+        <v>665</v>
+      </c>
+      <c r="D74" t="s">
+        <v>666</v>
+      </c>
+      <c r="E74" t="s">
+        <v>667</v>
+      </c>
+      <c r="F74" t="s">
+        <v>262</v>
+      </c>
+      <c r="G74" t="s">
+        <v>664</v>
+      </c>
+      <c r="H74" t="s">
+        <v>265</v>
+      </c>
+      <c r="I74" t="s">
+        <v>592</v>
+      </c>
+      <c r="J74" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>668</v>
+      </c>
+      <c r="B75" t="s">
+        <v>546</v>
+      </c>
+      <c r="C75" t="s">
+        <v>669</v>
+      </c>
+      <c r="D75" t="s">
+        <v>670</v>
+      </c>
+      <c r="E75" t="s">
+        <v>671</v>
+      </c>
+      <c r="F75" t="s">
+        <v>263</v>
+      </c>
+      <c r="G75" t="s">
+        <v>668</v>
+      </c>
+      <c r="H75" t="s">
+        <v>267</v>
+      </c>
+      <c r="J75" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>673</v>
+      </c>
+      <c r="B76" t="s">
+        <v>601</v>
+      </c>
+      <c r="C76" t="s">
+        <v>674</v>
+      </c>
+      <c r="D76" t="s">
+        <v>675</v>
+      </c>
+      <c r="E76" t="s">
+        <v>676</v>
+      </c>
+      <c r="F76" t="s">
+        <v>262</v>
+      </c>
+      <c r="G76" t="s">
+        <v>673</v>
+      </c>
+      <c r="H76" t="s">
+        <v>268</v>
+      </c>
+      <c r="I76" t="s">
+        <v>677</v>
+      </c>
+      <c r="J76" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>679</v>
+      </c>
+      <c r="B77" t="s">
+        <v>546</v>
+      </c>
+      <c r="C77" t="s">
+        <v>680</v>
+      </c>
+      <c r="D77" t="s">
+        <v>681</v>
+      </c>
+      <c r="E77" t="s">
+        <v>682</v>
+      </c>
+      <c r="F77" t="s">
+        <v>263</v>
+      </c>
+      <c r="G77" t="s">
+        <v>679</v>
+      </c>
+      <c r="H77" t="s">
+        <v>265</v>
+      </c>
+      <c r="I77" t="s">
+        <v>267</v>
+      </c>
+      <c r="J77" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>684</v>
+      </c>
+      <c r="B78" t="s">
+        <v>539</v>
+      </c>
+      <c r="C78" t="s">
+        <v>685</v>
+      </c>
+      <c r="D78" t="s">
+        <v>686</v>
+      </c>
+      <c r="E78" t="s">
+        <v>687</v>
+      </c>
+      <c r="F78" t="s">
+        <v>262</v>
+      </c>
+      <c r="G78" t="s">
+        <v>684</v>
+      </c>
+      <c r="H78" t="s">
+        <v>268</v>
+      </c>
+      <c r="I78" t="s">
+        <v>688</v>
+      </c>
+      <c r="J78" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>690</v>
+      </c>
+      <c r="B79" t="s">
+        <v>546</v>
+      </c>
+      <c r="C79" t="s">
+        <v>691</v>
+      </c>
+      <c r="D79" t="s">
+        <v>692</v>
+      </c>
+      <c r="F79" t="s">
+        <v>263</v>
+      </c>
+      <c r="G79" t="s">
+        <v>690</v>
+      </c>
+      <c r="H79" t="s">
+        <v>267</v>
+      </c>
+      <c r="J79" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>694</v>
+      </c>
+      <c r="B80" t="s">
+        <v>649</v>
+      </c>
+      <c r="C80" t="s">
+        <v>695</v>
+      </c>
+      <c r="D80" t="s">
+        <v>696</v>
+      </c>
+      <c r="E80" t="s">
+        <v>697</v>
+      </c>
+      <c r="F80" t="s">
+        <v>262</v>
+      </c>
+      <c r="G80" t="s">
+        <v>694</v>
+      </c>
+      <c r="H80" t="s">
+        <v>268</v>
+      </c>
+      <c r="I80" t="s">
+        <v>698</v>
+      </c>
+      <c r="J80" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>700</v>
+      </c>
+      <c r="B81">
+        <v>8.5</v>
+      </c>
+      <c r="C81" t="s">
+        <v>701</v>
+      </c>
+      <c r="D81" t="s">
+        <v>702</v>
+      </c>
+      <c r="E81" t="s">
+        <v>703</v>
+      </c>
+      <c r="F81" t="s">
+        <v>263</v>
+      </c>
+      <c r="G81" t="s">
+        <v>700</v>
+      </c>
+      <c r="H81" t="s">
+        <v>267</v>
+      </c>
+      <c r="J81" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>705</v>
+      </c>
+      <c r="B82" t="s">
+        <v>601</v>
+      </c>
+      <c r="C82" t="s">
+        <v>706</v>
+      </c>
+      <c r="D82" t="s">
+        <v>707</v>
+      </c>
+      <c r="E82" t="s">
+        <v>708</v>
+      </c>
+      <c r="F82" t="s">
+        <v>262</v>
+      </c>
+      <c r="G82" t="s">
+        <v>705</v>
+      </c>
+      <c r="H82" t="s">
+        <v>268</v>
+      </c>
+      <c r="I82" t="s">
+        <v>709</v>
+      </c>
+      <c r="J82" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>711</v>
+      </c>
+      <c r="B83" t="s">
+        <v>546</v>
+      </c>
+      <c r="C83" t="s">
+        <v>712</v>
+      </c>
+      <c r="D83" t="s">
+        <v>713</v>
+      </c>
+      <c r="E83" t="s">
+        <v>714</v>
+      </c>
+      <c r="F83" t="s">
+        <v>263</v>
+      </c>
+      <c r="G83" t="s">
+        <v>711</v>
+      </c>
+      <c r="H83" t="s">
+        <v>267</v>
+      </c>
+      <c r="J83" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>716</v>
+      </c>
+      <c r="B84" t="s">
+        <v>546</v>
+      </c>
+      <c r="C84" t="s">
+        <v>717</v>
+      </c>
+      <c r="D84" t="s">
+        <v>718</v>
+      </c>
+      <c r="E84" t="s">
+        <v>719</v>
+      </c>
+      <c r="F84" t="s">
+        <v>263</v>
+      </c>
+      <c r="G84" t="s">
+        <v>716</v>
+      </c>
+      <c r="H84" t="s">
+        <v>267</v>
+      </c>
+      <c r="J84" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>721</v>
+      </c>
+      <c r="B85" t="s">
+        <v>546</v>
+      </c>
+      <c r="C85" t="s">
+        <v>722</v>
+      </c>
+      <c r="D85" t="s">
+        <v>723</v>
+      </c>
+      <c r="E85" t="s">
+        <v>724</v>
+      </c>
+      <c r="F85" t="s">
+        <v>263</v>
+      </c>
+      <c r="G85" t="s">
+        <v>721</v>
+      </c>
+      <c r="H85" t="s">
+        <v>267</v>
+      </c>
+      <c r="J85" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>726</v>
+      </c>
+      <c r="B86" t="s">
+        <v>546</v>
+      </c>
+      <c r="C86" t="s">
+        <v>727</v>
+      </c>
+      <c r="D86" t="s">
+        <v>728</v>
+      </c>
+      <c r="E86" t="s">
+        <v>729</v>
+      </c>
+      <c r="F86" t="s">
+        <v>263</v>
+      </c>
+      <c r="G86" t="s">
+        <v>726</v>
+      </c>
+      <c r="H86" t="s">
+        <v>267</v>
+      </c>
+      <c r="J86" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>731</v>
+      </c>
+      <c r="B87" t="s">
+        <v>546</v>
+      </c>
+      <c r="C87" t="s">
+        <v>732</v>
+      </c>
+      <c r="D87" t="s">
+        <v>733</v>
+      </c>
+      <c r="E87" t="s">
+        <v>734</v>
+      </c>
+      <c r="F87" t="s">
+        <v>263</v>
+      </c>
+      <c r="G87" t="s">
+        <v>731</v>
+      </c>
+      <c r="H87" t="s">
+        <v>265</v>
+      </c>
+      <c r="I87" t="s">
+        <v>735</v>
+      </c>
+      <c r="J87" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>737</v>
+      </c>
+      <c r="B88" t="s">
+        <v>546</v>
+      </c>
+      <c r="C88" t="s">
+        <v>738</v>
+      </c>
+      <c r="D88" t="s">
+        <v>739</v>
+      </c>
+      <c r="F88" t="s">
+        <v>263</v>
+      </c>
+      <c r="G88" t="s">
+        <v>737</v>
+      </c>
+      <c r="H88" t="s">
+        <v>265</v>
+      </c>
+      <c r="I88" t="s">
+        <v>740</v>
+      </c>
+      <c r="J88" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>742</v>
+      </c>
+      <c r="B89" t="s">
+        <v>546</v>
+      </c>
+      <c r="C89" t="s">
+        <v>743</v>
+      </c>
+      <c r="D89" t="s">
+        <v>744</v>
+      </c>
+      <c r="E89" t="s">
+        <v>745</v>
+      </c>
+      <c r="F89" t="s">
+        <v>262</v>
+      </c>
+      <c r="G89" t="s">
+        <v>742</v>
+      </c>
+      <c r="H89" t="s">
+        <v>265</v>
+      </c>
+      <c r="I89" t="s">
+        <v>271</v>
+      </c>
+      <c r="J89" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>747</v>
+      </c>
+      <c r="B90" t="s">
+        <v>539</v>
+      </c>
+      <c r="C90" t="s">
+        <v>748</v>
+      </c>
+      <c r="D90" t="s">
+        <v>749</v>
+      </c>
+      <c r="E90" t="s">
+        <v>750</v>
+      </c>
+      <c r="F90" t="s">
+        <v>262</v>
+      </c>
+      <c r="G90" t="s">
+        <v>747</v>
+      </c>
+      <c r="H90" t="s">
+        <v>265</v>
+      </c>
+      <c r="I90" t="s">
+        <v>271</v>
+      </c>
+      <c r="J90" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>752</v>
+      </c>
+      <c r="B91" t="s">
+        <v>643</v>
+      </c>
+      <c r="C91" t="s">
+        <v>753</v>
+      </c>
+      <c r="D91" t="s">
+        <v>754</v>
+      </c>
+      <c r="E91" t="s">
+        <v>755</v>
+      </c>
+      <c r="F91" t="s">
+        <v>263</v>
+      </c>
+      <c r="G91" t="s">
+        <v>752</v>
+      </c>
+      <c r="H91" t="s">
+        <v>267</v>
+      </c>
+      <c r="J91" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>757</v>
+      </c>
+      <c r="B92" t="s">
+        <v>546</v>
+      </c>
+      <c r="C92" t="s">
+        <v>758</v>
+      </c>
+      <c r="D92" t="s">
+        <v>759</v>
+      </c>
+      <c r="E92" t="s">
+        <v>760</v>
+      </c>
+      <c r="F92" t="s">
+        <v>263</v>
+      </c>
+      <c r="G92" t="s">
+        <v>757</v>
+      </c>
+      <c r="H92" t="s">
+        <v>267</v>
+      </c>
+      <c r="J92" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>762</v>
+      </c>
+      <c r="B93" t="s">
+        <v>546</v>
+      </c>
+      <c r="C93" t="s">
+        <v>763</v>
+      </c>
+      <c r="D93" t="s">
+        <v>764</v>
+      </c>
+      <c r="E93" t="s">
+        <v>765</v>
+      </c>
+      <c r="F93" t="s">
+        <v>263</v>
+      </c>
+      <c r="G93" t="s">
+        <v>762</v>
+      </c>
+      <c r="H93" t="s">
+        <v>267</v>
+      </c>
+      <c r="J93" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>767</v>
+      </c>
+      <c r="B94" t="s">
+        <v>546</v>
+      </c>
+      <c r="C94" t="s">
+        <v>768</v>
+      </c>
+      <c r="D94" t="s">
+        <v>769</v>
+      </c>
+      <c r="E94" t="s">
+        <v>770</v>
+      </c>
+      <c r="F94" t="s">
+        <v>263</v>
+      </c>
+      <c r="G94" t="s">
+        <v>767</v>
+      </c>
+      <c r="H94" t="s">
+        <v>267</v>
+      </c>
+      <c r="J94" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>772</v>
+      </c>
+      <c r="B95">
+        <v>8</v>
+      </c>
+      <c r="C95" t="s">
+        <v>773</v>
+      </c>
+      <c r="D95" t="s">
+        <v>774</v>
+      </c>
+      <c r="E95" t="s">
+        <v>775</v>
+      </c>
+      <c r="F95" t="s">
+        <v>262</v>
+      </c>
+      <c r="G95" t="s">
+        <v>772</v>
+      </c>
+      <c r="H95" t="s">
+        <v>265</v>
+      </c>
+      <c r="I95" t="s">
+        <v>776</v>
+      </c>
+      <c r="J95" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>778</v>
+      </c>
+      <c r="B96" t="s">
+        <v>601</v>
+      </c>
+      <c r="C96" t="s">
+        <v>779</v>
+      </c>
+      <c r="D96" t="s">
+        <v>780</v>
+      </c>
+      <c r="E96" t="s">
+        <v>781</v>
+      </c>
+      <c r="F96" t="s">
+        <v>262</v>
+      </c>
+      <c r="G96" t="s">
+        <v>778</v>
+      </c>
+      <c r="H96" t="s">
+        <v>266</v>
+      </c>
+      <c r="I96" t="s">
+        <v>782</v>
+      </c>
+      <c r="J96" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>783</v>
+      </c>
+      <c r="B97" t="s">
+        <v>546</v>
+      </c>
+      <c r="C97" t="s">
+        <v>784</v>
+      </c>
+      <c r="D97" t="s">
+        <v>785</v>
+      </c>
+      <c r="E97" t="s">
+        <v>786</v>
+      </c>
+      <c r="F97" t="s">
+        <v>263</v>
+      </c>
+      <c r="G97" t="s">
+        <v>783</v>
+      </c>
+      <c r="H97" t="s">
+        <v>267</v>
+      </c>
+      <c r="J97" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>788</v>
+      </c>
+      <c r="B98" t="s">
+        <v>649</v>
+      </c>
+      <c r="C98" t="s">
+        <v>789</v>
+      </c>
+      <c r="D98" t="s">
+        <v>790</v>
+      </c>
+      <c r="E98" t="s">
+        <v>791</v>
+      </c>
+      <c r="F98" t="s">
+        <v>262</v>
+      </c>
+      <c r="G98" t="s">
+        <v>788</v>
+      </c>
+      <c r="H98" t="s">
+        <v>266</v>
+      </c>
+      <c r="I98" t="s">
+        <v>792</v>
+      </c>
+      <c r="J98" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>794</v>
+      </c>
+      <c r="B99" t="s">
+        <v>546</v>
+      </c>
+      <c r="C99" t="s">
+        <v>795</v>
+      </c>
+      <c r="D99" t="s">
+        <v>796</v>
+      </c>
+      <c r="E99" t="s">
+        <v>797</v>
+      </c>
+      <c r="F99" t="s">
+        <v>262</v>
+      </c>
+      <c r="G99" t="s">
+        <v>794</v>
+      </c>
+      <c r="H99" t="s">
+        <v>267</v>
+      </c>
+      <c r="J99" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>799</v>
+      </c>
+      <c r="B100" t="s">
+        <v>649</v>
+      </c>
+      <c r="C100" t="s">
+        <v>800</v>
+      </c>
+      <c r="D100" t="s">
+        <v>801</v>
+      </c>
+      <c r="E100" t="s">
+        <v>802</v>
+      </c>
+      <c r="F100" t="s">
+        <v>262</v>
+      </c>
+      <c r="G100" t="s">
+        <v>799</v>
+      </c>
+      <c r="H100" t="s">
+        <v>268</v>
+      </c>
+      <c r="I100" t="s">
+        <v>803</v>
+      </c>
+      <c r="J100" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>805</v>
+      </c>
+      <c r="B101" t="s">
+        <v>601</v>
+      </c>
+      <c r="C101" t="s">
+        <v>806</v>
+      </c>
+      <c r="D101" t="s">
+        <v>807</v>
+      </c>
+      <c r="E101" t="s">
+        <v>808</v>
+      </c>
+      <c r="F101" t="s">
+        <v>262</v>
+      </c>
+      <c r="G101" t="s">
+        <v>805</v>
+      </c>
+      <c r="H101" t="s">
+        <v>268</v>
+      </c>
+      <c r="I101" t="s">
+        <v>809</v>
+      </c>
+      <c r="J101" t="s">
+        <v>810</v>
       </c>
     </row>
   </sheetData>
